--- a/AAII_Financials/Quarterly/BBIO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BBIO_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="92">
   <si>
     <t>BBIO</t>
   </si>
@@ -656,188 +656,191 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E8" s="3">
         <v>4100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>73700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>12900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>54000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8100</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S8" s="3">
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T8" s="3">
         <v>13800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>26700</v>
       </c>
-      <c r="U8" s="3">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W8" s="3">
-        <v>0</v>
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+      <c r="W8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X8" s="3">
         <v>0</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
+      <c r="Y8" s="3">
+        <v>0</v>
       </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
@@ -845,8 +848,11 @@
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -857,32 +863,32 @@
         <v>600</v>
       </c>
       <c r="F9" s="3">
+        <v>600</v>
+      </c>
+      <c r="G9" s="3">
         <v>700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>600</v>
-      </c>
-      <c r="H9" s="3">
-        <v>700</v>
       </c>
       <c r="I9" s="3">
         <v>700</v>
       </c>
       <c r="J9" s="3">
+        <v>700</v>
+      </c>
+      <c r="K9" s="3">
         <v>1300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>100</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
@@ -898,12 +904,12 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T9" s="3">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U9" s="3">
         <v>2500</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
@@ -922,44 +928,47 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E10" s="3">
         <v>3500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>73000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>11300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>53900</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
@@ -975,12 +984,12 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T10" s="3">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U10" s="3">
         <v>24200</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
@@ -999,8 +1008,11 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1028,85 +1040,89 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>130200</v>
+      </c>
+      <c r="E12" s="3">
         <v>125100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>107500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>92900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>90900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>92500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>108400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>107600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>122200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>104300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>102000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>122600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>90200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>92100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>86600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>68200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>57500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>55300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>95200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>42900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>51200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>31100</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1182,35 +1198,38 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>800</v>
+      </c>
+      <c r="E14" s="3">
         <v>300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>7700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>5000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>8400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>22700</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1232,26 +1251,26 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>400</v>
-      </c>
-      <c r="U14" s="3">
-        <v>2000</v>
       </c>
       <c r="V14" s="3">
         <v>2000</v>
       </c>
       <c r="W14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="X14" s="3">
         <v>-19300</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>3</v>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>3</v>
@@ -1259,8 +1278,11 @@
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1336,8 +1358,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1362,162 +1387,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>179200</v>
+      </c>
+      <c r="E17" s="3">
         <v>161800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>147700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>128000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>131100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>129500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>153900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>175400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>178500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>151800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>148000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>168000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>127600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>128100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>124600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>102500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>92500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>81700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>133100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>63800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>46300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>41500</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-177500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-157700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-146100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-126200</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-129200</v>
       </c>
       <c r="H18" s="3">
         <v>-129200</v>
       </c>
       <c r="I18" s="3">
+        <v>-129200</v>
+      </c>
+      <c r="J18" s="3">
         <v>-80200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-173700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-165600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-149500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-94000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-167500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-127500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-120000</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T18" s="3">
         <v>-78700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-55000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-133100</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X18" s="3">
         <v>-46300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-41500</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1545,118 +1577,122 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>27400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>6000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>8600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>8800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>97900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-7300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>28500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>6100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>3400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>700</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S20" s="3">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T20" s="3">
         <v>-2500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-3600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-7100</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X20" s="3">
         <v>-1800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>500</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-148500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-157500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-138500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-121000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-118900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-118700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>19300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-179100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-135600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-149700</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1675,15 +1711,15 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3">
         <v>-58200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-139900</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1699,8 +1735,11 @@
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1708,67 +1747,67 @@
         <v>20300</v>
       </c>
       <c r="E22" s="3">
+        <v>20300</v>
+      </c>
+      <c r="F22" s="3">
         <v>20600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>20100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>20000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>19800</v>
-      </c>
-      <c r="I22" s="3">
-        <v>20300</v>
       </c>
       <c r="J22" s="3">
         <v>20300</v>
       </c>
       <c r="K22" s="3">
+        <v>20300</v>
+      </c>
+      <c r="L22" s="3">
         <v>15100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>11100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>10800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>9700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>11000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>10900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>10800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>4000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>3000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>2100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>3600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1700</v>
-      </c>
-      <c r="W22" s="3">
-        <v>1200</v>
       </c>
       <c r="X22" s="3">
         <v>1200</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
+      <c r="Y22" s="3">
+        <v>1200</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>3</v>
@@ -1776,85 +1815,91 @@
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-170300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-179500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-160700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-142700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-140600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-140200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-201300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-152300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-161000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-102100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-171100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-135000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-130200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-136200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-104100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-84200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-60700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-143800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-69400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-49200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-42100</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1930,8 +1975,11 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2007,162 +2055,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-170300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-179500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-160700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-142700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-140600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-140200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-201300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-152300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-161000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-102100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-171100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-135000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-130200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-136200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-104100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-84200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-60700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-143800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-69400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-49200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-42100</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-168100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-177000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-157900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-140200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-137600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-137300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-9900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-196400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-147200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-155900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-96300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-163100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-120000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-115900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-121000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-91900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-73500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-60000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-127100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-61200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-31400</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2238,8 +2295,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2315,8 +2375,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2392,8 +2455,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2469,162 +2535,171 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-27400</v>
+      </c>
+      <c r="E32" s="3">
         <v>1500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-6000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-8600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-8800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-97900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>7300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-28500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-6100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-3400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-700</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S32" s="3">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T32" s="3">
         <v>2500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>3600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>7100</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X32" s="3">
         <v>1800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-500</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-168100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-177000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-157900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-140200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-137600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-137300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-9900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-196400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-147200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-155900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-96300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-163100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-120000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-115900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-121000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-91900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-73500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-60000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-127100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-61200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-31400</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2700,167 +2775,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-168100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-177000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-157900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-140200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-137600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-137300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-9900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-196400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-147200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-155900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-96300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-163100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-120000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-115900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-121000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-91900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-73500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-60000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-127100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-61200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-31400</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2888,8 +2972,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2917,71 +3002,72 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>375900</v>
+      </c>
+      <c r="E41" s="3">
         <v>505200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>302400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>407400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>376700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>483200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>470100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>371600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>393800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>180300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>378400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>471200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>356100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>367000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>540900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>757000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>363800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>414000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>293800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>373000</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2994,65 +3080,68 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>58900</v>
+      </c>
+      <c r="E42" s="3">
         <v>38100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>81400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>83900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>95200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>108700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>245600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>299700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>442900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>419300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>459200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>447900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>251000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>343700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>300000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>148100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>182200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>122100</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3071,8 +3160,11 @@
       <c r="AA42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3097,27 +3189,27 @@
       <c r="J43" s="3">
         <v>0</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L43" s="3">
+      <c r="K43" s="3">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3">
         <v>500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>10200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>500</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P43" s="3">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3">
         <v>8000</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3133,8 +3225,8 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W43" s="3">
-        <v>0</v>
+      <c r="W43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X43" s="3">
         <v>0</v>
@@ -3148,8 +3240,11 @@
       <c r="AA43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3225,71 +3320,74 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>42700</v>
+      </c>
+      <c r="E45" s="3">
         <v>44400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>49100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>61400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>76900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>50200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>55600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>45000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>52200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>39600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>62000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>25500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>35700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>26700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>21000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>19800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>22600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>22100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>12900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>9400</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3302,71 +3400,74 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>477600</v>
+      </c>
+      <c r="E46" s="3">
         <v>587700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>432900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>552700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>548900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>642200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>771300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>716200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>888900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>639700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>909900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>945100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>642800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>745400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>861900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>925000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>568600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>558200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>306700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>382500</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3379,8 +3480,11 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3405,45 +3509,45 @@
       <c r="J47" s="3">
         <v>0</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L47" s="3">
+      <c r="K47" s="3">
+        <v>0</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3">
         <v>17700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>79600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>82200</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R47" s="3">
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S47" s="3">
         <v>23200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>31100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>76800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>7500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>12500</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3456,70 +3560,73 @@
       <c r="AA47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E48" s="3">
         <v>21700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>22900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>24100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>25200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>27300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>29700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>31100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>46000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>44800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>42200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>35800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>36800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>25800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>26000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>24600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3000</v>
-      </c>
-      <c r="U48" s="3">
-        <v>1900</v>
       </c>
       <c r="V48" s="3">
         <v>1900</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
+      <c r="W48" s="3">
+        <v>1900</v>
       </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
@@ -3533,41 +3640,44 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E49" s="3">
         <v>26900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>27500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>28100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>28700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>29300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>29900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>30500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>44900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>46200</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3583,8 +3693,8 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
+      <c r="S49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T49" s="3">
         <v>0</v>
@@ -3610,8 +3720,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3687,8 +3800,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3764,71 +3880,74 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E52" s="3">
         <v>18700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>20400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>20800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>20200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>29900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>31300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>35300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>33000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>33100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>49800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>30200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>23900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>16500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>17300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>17000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>26300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>9500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4600</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3841,8 +3960,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3918,71 +4040,74 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>546400</v>
+      </c>
+      <c r="E54" s="3">
         <v>655000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>503700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>625700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>623000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>728700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>862200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>813100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1012800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>781500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1081500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1093300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>703600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>787700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>905200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>989800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>631700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>640500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>325500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>401400</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3995,8 +4120,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4024,8 +4152,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4053,71 +4182,72 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E57" s="3">
         <v>4500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>11600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>10200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>12000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>22300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>9800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>12800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>13100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>8900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>10300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>16100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>12300</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4130,34 +4260,37 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K58" s="3">
-        <v>300</v>
+      <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L58" s="3">
         <v>300</v>
@@ -4166,14 +4299,14 @@
         <v>300</v>
       </c>
       <c r="N58" s="3">
+        <v>300</v>
+      </c>
+      <c r="O58" s="3">
         <v>3800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1600</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4189,8 +4322,8 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
+      <c r="V58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
@@ -4207,71 +4340,74 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>133200</v>
+      </c>
+      <c r="E59" s="3">
         <v>101600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>106200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>92500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>109900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>109000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>132400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>93400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>122900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>83500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>109300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>80500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>85100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>65900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>79800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>51800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>51500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>29600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>22600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>23100</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4284,71 +4420,74 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>143800</v>
+      </c>
+      <c r="E60" s="3">
         <v>106100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>110100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>96600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>121400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>119200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>141200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>103500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>135100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>95800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>131900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>94700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>95600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>75700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>92600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>64900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>60400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>39900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>38700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>35500</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4361,71 +4500,74 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1726700</v>
+      </c>
+      <c r="E61" s="3">
         <v>1721100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1718900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1713300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1707600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1698700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1693200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1708100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1705100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1376600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1375300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1362700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>477400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>471900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>466600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>461300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>91800</v>
-      </c>
-      <c r="T61" s="3">
-        <v>75000</v>
       </c>
       <c r="U61" s="3">
         <v>75000</v>
       </c>
       <c r="V61" s="3">
+        <v>75000</v>
+      </c>
+      <c r="W61" s="3">
         <v>54900</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4438,71 +4580,74 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E62" s="3">
         <v>21600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>24200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>29400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>38900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>41200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>42900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>42300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>38300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>44900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>29900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>24000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>22600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>21700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>18500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>11500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>400</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4515,8 +4660,11 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4592,8 +4740,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4669,8 +4820,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4746,71 +4900,74 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1900600</v>
+      </c>
+      <c r="E66" s="3">
         <v>1862600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1865700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1851300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1877700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1867200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1887800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1854100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1883200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1524900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1545800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1488600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>645700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>623900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>639500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>609100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>223200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>180800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>162600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>149200</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4823,8 +4980,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4852,8 +5012,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4929,8 +5090,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5006,8 +5170,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5063,13 +5230,13 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
-        <v>479000</v>
+        <v>0</v>
       </c>
       <c r="V70" s="3">
         <v>479000</v>
       </c>
       <c r="W70" s="3">
-        <v>0</v>
+        <v>479000</v>
       </c>
       <c r="X70" s="3">
         <v>0</v>
@@ -5083,8 +5250,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5160,71 +5330,74 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2560500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2392400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2215400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2057500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1918100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1780600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1643200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1633400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1437000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1289800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1133900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1037500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-888800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-768800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-652900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-531900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-440000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-366600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-319500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-230300</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5237,8 +5410,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5314,8 +5490,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5391,8 +5570,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5468,71 +5650,74 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1354300</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1207500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1362000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-1225700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-1254600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-1138400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-1025500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-1041000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-870400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-743400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-464300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-395300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>57900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>163800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>265800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>380700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>408500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>459800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-316100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-226900</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5545,8 +5730,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5622,167 +5810,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-168100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-177000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-157900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-140200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-137600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-137300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-9900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-196400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-147200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-155900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-96300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-163100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-120000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-115900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-121000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-91900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-73500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-60000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-127100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-61200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-31400</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5810,8 +6007,9 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5825,26 +6023,26 @@
         <v>1600</v>
       </c>
       <c r="G83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H83" s="3">
         <v>1700</v>
-      </c>
-      <c r="H83" s="3">
-        <v>1600</v>
       </c>
       <c r="I83" s="3">
         <v>1600</v>
       </c>
       <c r="J83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K83" s="3">
         <v>1900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>300</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5863,18 +6061,18 @@
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T83" s="3">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U83" s="3">
         <v>400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>100</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5887,8 +6085,11 @@
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5964,8 +6165,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6041,8 +6245,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6118,8 +6325,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6195,8 +6405,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6272,71 +6485,74 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-124800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-145200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-113400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-144300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-93200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-135200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-30500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-160600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-133900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-121600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-91700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-150800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-96300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-131700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-87800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-83900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-76200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-50000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-127400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-59100</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6349,8 +6565,11 @@
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6378,8 +6597,9 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6390,59 +6610,59 @@
         <v>-400</v>
       </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="G91" s="3">
-        <v>-800</v>
+        <v>0</v>
       </c>
       <c r="H91" s="3">
         <v>-800</v>
       </c>
       <c r="I91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="J91" s="3">
         <v>-3900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-400</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6455,8 +6675,11 @@
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6532,8 +6755,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6609,71 +6835,74 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E94" s="3">
         <v>37700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>4100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>12300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>18000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>146900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>149700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>138600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>21800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>59000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-282100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>83000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-45100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-129000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>38000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-16900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-197300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2400</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6686,8 +6915,11 @@
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6715,8 +6947,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6792,8 +7025,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6869,8 +7105,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6946,8 +7185,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7023,71 +7265,74 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E100" s="3">
         <v>307000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>150200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>6400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-20800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>325400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-135500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>547900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>4500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>439200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>42900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>367500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-11600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1700</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7100,8 +7345,11 @@
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7177,71 +7425,74 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-129400</v>
+      </c>
+      <c r="E102" s="3">
         <v>199500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-110500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>18200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-68900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>13100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>98500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-22200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>213300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-198000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-92600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>115100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-8700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-174000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-216100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>393300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-50200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>120200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-142000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-63200</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7252,6 +7503,9 @@
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BBIO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BBIO_QTR_FIN.xlsx
@@ -656,194 +656,198 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>211100</v>
+      </c>
+      <c r="E8" s="3">
         <v>1700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>73700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>12900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>54000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>8100</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T8" s="3">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U8" s="3">
         <v>13800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>26700</v>
       </c>
-      <c r="V8" s="3">
-        <v>0</v>
-      </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X8" s="3">
-        <v>0</v>
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+      <c r="X8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y8" s="3">
         <v>0</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>3</v>
+      <c r="Z8" s="3">
+        <v>0</v>
       </c>
       <c r="AA8" s="3" t="s">
         <v>3</v>
@@ -851,8 +855,11 @@
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -866,32 +873,32 @@
         <v>600</v>
       </c>
       <c r="G9" s="3">
+        <v>600</v>
+      </c>
+      <c r="H9" s="3">
         <v>700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>600</v>
-      </c>
-      <c r="I9" s="3">
-        <v>700</v>
       </c>
       <c r="J9" s="3">
         <v>700</v>
       </c>
       <c r="K9" s="3">
+        <v>700</v>
+      </c>
+      <c r="L9" s="3">
         <v>1300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>100</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
@@ -907,12 +914,12 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U9" s="3">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V9" s="3">
         <v>2500</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
@@ -931,47 +938,50 @@
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>210500</v>
+      </c>
+      <c r="E10" s="3">
         <v>1100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>73000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>11300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>53900</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
@@ -987,12 +997,12 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U10" s="3">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V10" s="3">
         <v>24200</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1011,8 +1021,11 @@
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1041,88 +1054,92 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>141000</v>
+      </c>
+      <c r="E12" s="3">
         <v>130200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>125100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>107500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>92900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>90900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>92500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>108400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>107600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>122200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>104300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>102000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>122600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>90200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>92100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>86600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>68200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>57500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>55300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>95200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>42900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>51200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>31100</v>
       </c>
-      <c r="Z12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1201,38 +1218,41 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E14" s="3">
         <v>800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>3400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>7700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>5000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>8400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>22700</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1254,26 +1274,26 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>400</v>
-      </c>
-      <c r="V14" s="3">
-        <v>2000</v>
       </c>
       <c r="W14" s="3">
         <v>2000</v>
       </c>
       <c r="X14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Y14" s="3">
         <v>-19300</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>3</v>
+      <c r="Z14" s="3">
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>3</v>
@@ -1281,8 +1301,11 @@
       <c r="AB14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1361,8 +1384,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1388,168 +1414,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>237400</v>
+      </c>
+      <c r="E17" s="3">
         <v>179200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>161800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>147700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>128000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>131100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>129500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>153900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>175400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>178500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>151800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>148000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>168000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>127600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>128100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>124600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>102500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>92500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>81700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>133100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>63800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>46300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>41500</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-26300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-177500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-157700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-146100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-126200</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-129200</v>
       </c>
       <c r="I18" s="3">
         <v>-129200</v>
       </c>
       <c r="J18" s="3">
+        <v>-129200</v>
+      </c>
+      <c r="K18" s="3">
         <v>-80200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-173700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-165600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-149500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-94000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-167500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-127500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-120000</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T18" s="3">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U18" s="3">
         <v>-78700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-55000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-133100</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X18" s="3">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-46300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-41500</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1578,124 +1611,128 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E20" s="3">
         <v>27400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>6000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>8600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>8800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>97900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-7300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>28500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>6100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>700</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T20" s="3">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U20" s="3">
         <v>-2500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-3600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-7100</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>500</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-148500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-157500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-138500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-121000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-118900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-118700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>19300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-179100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-135600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-149700</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1714,15 +1751,15 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3">
         <v>-58200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-139900</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1738,79 +1775,82 @@
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>20300</v>
+        <v>23500</v>
       </c>
       <c r="E22" s="3">
         <v>20300</v>
       </c>
       <c r="F22" s="3">
+        <v>20300</v>
+      </c>
+      <c r="G22" s="3">
         <v>20600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>20100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>20000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>19800</v>
-      </c>
-      <c r="J22" s="3">
-        <v>20300</v>
       </c>
       <c r="K22" s="3">
         <v>20300</v>
       </c>
       <c r="L22" s="3">
+        <v>20300</v>
+      </c>
+      <c r="M22" s="3">
         <v>15100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>11100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>10800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>9700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>11000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>10900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>10800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>4000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>3000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>2100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>3600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1700</v>
-      </c>
-      <c r="X22" s="3">
-        <v>1200</v>
       </c>
       <c r="Y22" s="3">
         <v>1200</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>3</v>
+      <c r="Z22" s="3">
+        <v>1200</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>3</v>
@@ -1818,88 +1858,94 @@
       <c r="AB22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-36200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-170300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-179500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-160700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-142700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-140600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-140200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-201300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-152300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-161000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-102100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-171100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-135000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-130200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-136200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-104100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-84200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-60700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-143800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-69400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-49200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-42100</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1978,8 +2024,11 @@
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2058,168 +2107,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-36200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-170300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-179500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-160700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-142700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-140600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-140200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-201300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-152300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-161000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-102100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-171100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-135000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-130200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-136200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-104100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-84200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-60700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-143800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-69400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-49200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-42100</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-35200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-168100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-177000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-157900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-140200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-137600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-137300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-9900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-196400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-147200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-155900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-96300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-163100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-120000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-115900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-121000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-91900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-73500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-60000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-127100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-61200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-31400</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2298,8 +2356,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2378,8 +2439,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2458,8 +2522,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2538,168 +2605,177 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-27400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-6000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-8600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-8800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-97900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>7300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-28500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-6100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-700</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T32" s="3">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U32" s="3">
         <v>2500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>3600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>7100</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X32" s="3">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y32" s="3">
         <v>1800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-500</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-35200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-168100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-177000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-157900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-140200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-137600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-137300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-9900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-196400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-147200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-155900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-96300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-163100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-120000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-115900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-121000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-91900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-73500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-60000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-127100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-61200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-31400</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2778,173 +2854,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-35200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-168100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-177000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-157900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-140200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-137600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-137300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-9900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-196400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-147200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-155900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-96300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-163100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-120000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-115900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-121000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-91900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-73500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-60000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-127100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-61200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-31400</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2973,8 +3058,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3003,74 +3089,75 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>475200</v>
+      </c>
+      <c r="E41" s="3">
         <v>375900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>505200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>302400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>407400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>376700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>483200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>470100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>371600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>393800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>180300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>378400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>471200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>356100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>367000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>540900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>757000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>363800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>414000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>293800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>373000</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3083,68 +3170,71 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>44500</v>
+      </c>
+      <c r="E42" s="3">
         <v>58900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>38100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>81400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>83900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>95200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>108700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>245600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>299700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>442900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>419300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>459200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>447900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>251000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>343700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>300000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>148100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>182200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>122100</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3163,8 +3253,11 @@
       <c r="AB42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3192,27 +3285,27 @@
       <c r="K43" s="3">
         <v>0</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M43" s="3">
+      <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3">
         <v>500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>10200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>500</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q43" s="3">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3">
         <v>8000</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3228,8 +3321,8 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X43" s="3">
-        <v>0</v>
+      <c r="X43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y43" s="3">
         <v>0</v>
@@ -3243,8 +3336,11 @@
       <c r="AB43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3323,74 +3419,77 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>263700</v>
+      </c>
+      <c r="E45" s="3">
         <v>42700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>44400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>49100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>61400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>76900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>50200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>55600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>45000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>52200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>39600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>62000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>25500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>35700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>26700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>21000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>19800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>22600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>22100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>12900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>9400</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3403,74 +3502,77 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>783400</v>
+      </c>
+      <c r="E46" s="3">
         <v>477600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>587700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>432900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>552700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>548900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>642200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>771300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>716200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>888900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>639700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>909900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>945100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>642800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>745400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>861900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>925000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>568600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>558200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>306700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>382500</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3483,8 +3585,11 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3512,45 +3617,45 @@
       <c r="K47" s="3">
         <v>0</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M47" s="3">
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3">
         <v>17700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>79600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>82200</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S47" s="3">
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T47" s="3">
         <v>23200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>31100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>76800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>7500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>12500</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3563,73 +3668,76 @@
       <c r="AB47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E48" s="3">
         <v>19800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>21700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>22900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>24100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>25200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>27300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>29700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>31100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>46000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>44800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>42200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>35800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>36800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>25800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>26000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>24600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3000</v>
-      </c>
-      <c r="V48" s="3">
-        <v>1900</v>
       </c>
       <c r="W48" s="3">
         <v>1900</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
+      <c r="X48" s="3">
+        <v>1900</v>
       </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
@@ -3643,44 +3751,47 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>25700</v>
+      </c>
+      <c r="E49" s="3">
         <v>26300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>26900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>27500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>28100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>28700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>29300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>29900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>30500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>44900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>46200</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3696,8 +3807,8 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
+      <c r="T49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U49" s="3">
         <v>0</v>
@@ -3723,8 +3834,11 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3803,8 +3917,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3883,74 +4000,77 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E52" s="3">
         <v>22600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>18700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>20400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>20800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>20200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>29900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>31300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>35300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>33000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>33100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>49800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>30200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>23900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>16500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>17300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>17000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>26300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>9500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4600</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3963,8 +4083,11 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4043,74 +4166,77 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>849300</v>
+      </c>
+      <c r="E54" s="3">
         <v>546400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>655000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>503700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>625700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>623000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>728700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>862200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>813100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1012800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>781500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1081500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1093300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>703600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>787700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>905200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>989800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>631700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>640500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>325500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>401400</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4123,8 +4249,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4153,8 +4282,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4183,74 +4313,75 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E57" s="3">
         <v>10700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>11600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>10200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>12000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>22300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>9800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>12800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>13100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>8900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>10300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>16100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>12300</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4263,8 +4394,11 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4289,11 +4423,11 @@
       <c r="J58" s="3">
         <v>0</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3">
-        <v>300</v>
+      <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M58" s="3">
         <v>300</v>
@@ -4302,14 +4436,14 @@
         <v>300</v>
       </c>
       <c r="O58" s="3">
+        <v>300</v>
+      </c>
+      <c r="P58" s="3">
         <v>3800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1600</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4325,8 +4459,8 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
+      <c r="W58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X58" s="3">
         <v>0</v>
@@ -4343,74 +4477,77 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>136700</v>
+      </c>
+      <c r="E59" s="3">
         <v>133200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>101600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>106200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>92500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>109900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>109000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>132400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>93400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>122900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>83500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>109300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>80500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>85100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>65900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>79800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>51800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>51500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>29600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>22600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>23100</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4423,74 +4560,77 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>141500</v>
+      </c>
+      <c r="E60" s="3">
         <v>143800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>106100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>110100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>96600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>121400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>119200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>141200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>103500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>135100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>95800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>131900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>94700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>95600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>75700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>92600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>64900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>60400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>39900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>38700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>35500</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4503,74 +4643,77 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1715900</v>
+      </c>
+      <c r="E61" s="3">
         <v>1726700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1721100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1718900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1713300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1707600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1698700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1693200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1708100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1705100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1376600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1375300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1362700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>477400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>471900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>466600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>461300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>91800</v>
-      </c>
-      <c r="U61" s="3">
-        <v>75000</v>
       </c>
       <c r="V61" s="3">
         <v>75000</v>
       </c>
       <c r="W61" s="3">
+        <v>75000</v>
+      </c>
+      <c r="X61" s="3">
         <v>54900</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4583,74 +4726,77 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E62" s="3">
         <v>18300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>21600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>24200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>29400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>38900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>41200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>42900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>42300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>38300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>44900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>29900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>24000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>22600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>21700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>18500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>11500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>400</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4663,8 +4809,11 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4743,8 +4892,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4823,8 +4975,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4903,74 +5058,77 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1898900</v>
+      </c>
+      <c r="E66" s="3">
         <v>1900600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1862600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1865700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1851300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1877700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1867200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1887800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1854100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1883200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1524900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1545800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1488600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>645700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>623900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>639500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>609100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>223200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>180800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>162600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>149200</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4983,8 +5141,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5013,8 +5174,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5093,8 +5255,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5173,8 +5338,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5233,13 +5401,13 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
-        <v>479000</v>
+        <v>0</v>
       </c>
       <c r="W70" s="3">
         <v>479000</v>
       </c>
       <c r="X70" s="3">
-        <v>0</v>
+        <v>479000</v>
       </c>
       <c r="Y70" s="3">
         <v>0</v>
@@ -5253,8 +5421,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5333,74 +5504,77 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2595700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2560500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2392400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2215400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2057500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1918100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1780600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1643200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1633400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1437000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1289800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1133900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1037500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-888800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-768800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-652900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-531900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-440000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-366600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-319500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-230300</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5413,8 +5587,11 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5493,8 +5670,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5573,8 +5753,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5653,74 +5836,77 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1049500</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1354300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1207500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-1362000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-1225700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-1254600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-1138400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-1025500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-1041000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-870400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-743400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-464300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-395300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>57900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>163800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>265800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>380700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>408500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>459800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-316100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-226900</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5733,8 +5919,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5813,173 +6002,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-35200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-168100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-177000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-157900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-140200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-137600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-137300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-9900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-196400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-147200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-155900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-96300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-163100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-120000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-115900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-121000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-91900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-73500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-60000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-127100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-61200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-31400</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6008,8 +6206,9 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6026,26 +6225,26 @@
         <v>1600</v>
       </c>
       <c r="H83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I83" s="3">
         <v>1700</v>
-      </c>
-      <c r="I83" s="3">
-        <v>1600</v>
       </c>
       <c r="J83" s="3">
         <v>1600</v>
       </c>
       <c r="K83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L83" s="3">
         <v>1900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>300</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6064,18 +6263,18 @@
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U83" s="3">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V83" s="3">
         <v>400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>100</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6088,8 +6287,11 @@
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6168,8 +6370,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6248,8 +6453,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6328,8 +6536,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6408,8 +6619,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6488,74 +6702,77 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-219500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-124800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-145200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-113400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-144300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-93200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-135200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-30500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-160600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-133900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-121600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-91700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-150800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-96300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-131700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-87800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-83900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-76200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-50000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-127400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-59100</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6568,8 +6785,11 @@
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6598,13 +6818,14 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-400</v>
+        <v>-1500</v>
       </c>
       <c r="E91" s="3">
         <v>-400</v>
@@ -6613,59 +6834,59 @@
         <v>-400</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="H91" s="3">
-        <v>-800</v>
+        <v>0</v>
       </c>
       <c r="I91" s="3">
         <v>-800</v>
       </c>
       <c r="J91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="K91" s="3">
         <v>-3900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-400</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6678,8 +6899,11 @@
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6758,8 +6982,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6838,74 +7065,77 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>37700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>4100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>12300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>18000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>146900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>149700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>138600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>21800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>59000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-282100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>83000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-45100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-129000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>38000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-16900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-197300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2400</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6918,8 +7148,11 @@
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6948,8 +7181,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7028,8 +7262,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7108,8 +7345,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7188,8 +7428,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7268,74 +7511,77 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>279500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>307000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>150200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>6400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-20800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>325400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-135500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>547900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>4500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>439200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>42900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>367500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-11600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1700</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7348,8 +7594,11 @@
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7428,74 +7677,77 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>82800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-129400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>199500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-110500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>18200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-68900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>13100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>98500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-22200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>213300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-198000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-92600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>115100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-8700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-174000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-216100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>393300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-50200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>120200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-142000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-63200</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7506,6 +7758,9 @@
         <v>3</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BBIO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BBIO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="92">
   <si>
     <t>BBIO</t>
   </si>
@@ -656,201 +656,205 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E8" s="3">
         <v>211100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>73700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>12900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>54000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>8100</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U8" s="3">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V8" s="3">
         <v>13800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>26700</v>
       </c>
-      <c r="W8" s="3">
-        <v>0</v>
-      </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>0</v>
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z8" s="3">
         <v>0</v>
       </c>
-      <c r="AA8" s="3" t="s">
-        <v>3</v>
+      <c r="AA8" s="3">
+        <v>0</v>
       </c>
       <c r="AB8" s="3" t="s">
         <v>3</v>
@@ -858,8 +862,11 @@
       <c r="AC8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -876,32 +883,32 @@
         <v>600</v>
       </c>
       <c r="H9" s="3">
+        <v>600</v>
+      </c>
+      <c r="I9" s="3">
         <v>700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>600</v>
-      </c>
-      <c r="J9" s="3">
-        <v>700</v>
       </c>
       <c r="K9" s="3">
         <v>700</v>
       </c>
       <c r="L9" s="3">
+        <v>700</v>
+      </c>
+      <c r="M9" s="3">
         <v>1300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>100</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
@@ -917,12 +924,12 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V9" s="3">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W9" s="3">
         <v>2500</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
@@ -941,50 +948,53 @@
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E10" s="3">
         <v>210500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>73000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>11300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>53900</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1000,12 +1010,12 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V10" s="3">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W10" s="3">
         <v>24200</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1024,8 +1034,11 @@
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1055,91 +1068,95 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>114700</v>
+      </c>
+      <c r="E12" s="3">
         <v>141000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>130200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>125100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>107500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>92900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>90900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>92500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>108400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>107600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>122200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>104300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>102000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>122600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>90200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>92100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>86600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>68200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>57500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>55300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>95200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>42900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>51200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>31100</v>
       </c>
-      <c r="AA12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1221,41 +1238,44 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-123400</v>
+      </c>
+      <c r="E14" s="3">
         <v>30000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>3500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>7700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>5000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>8400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>22700</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1277,26 +1297,26 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>400</v>
-      </c>
-      <c r="W14" s="3">
-        <v>2000</v>
       </c>
       <c r="X14" s="3">
         <v>2000</v>
       </c>
       <c r="Y14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Z14" s="3">
         <v>-19300</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>3</v>
+      <c r="AA14" s="3">
+        <v>0</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>3</v>
@@ -1304,8 +1324,11 @@
       <c r="AC14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1387,8 +1410,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1415,174 +1441,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>51400</v>
+      </c>
+      <c r="E17" s="3">
         <v>237400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>179200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>161800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>147700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>128000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>131100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>129500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>153900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>175400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>178500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>151800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>148000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>168000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>127600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>128100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>124600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>102500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>92500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>81700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>133100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>63800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>46300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>41500</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-49200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-26300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-177500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-157700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-146100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-126200</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-129200</v>
       </c>
       <c r="J18" s="3">
         <v>-129200</v>
       </c>
       <c r="K18" s="3">
+        <v>-129200</v>
+      </c>
+      <c r="L18" s="3">
         <v>-80200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-173700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-165600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-149500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-94000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-167500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-127500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-120000</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V18" s="3">
         <v>-78700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-55000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-133100</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z18" s="3">
         <v>-46300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-41500</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1612,130 +1645,134 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E20" s="3">
         <v>13600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>27400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>6000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>8600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>8800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>97900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-7300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>28500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>6100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>3400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>700</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V20" s="3">
         <v>-2500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-3600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-7100</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>500</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-51000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-11100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-148500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-157500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-138500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-121000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-118900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-118700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>19300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-179100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-135600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-149700</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1754,15 +1791,15 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W21" s="3">
         <v>-58200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-139900</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1778,82 +1815,85 @@
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>22900</v>
+      </c>
+      <c r="E22" s="3">
         <v>23500</v>
-      </c>
-      <c r="E22" s="3">
-        <v>20300</v>
       </c>
       <c r="F22" s="3">
         <v>20300</v>
       </c>
       <c r="G22" s="3">
+        <v>20300</v>
+      </c>
+      <c r="H22" s="3">
         <v>20600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>20100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>20000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>19800</v>
-      </c>
-      <c r="K22" s="3">
-        <v>20300</v>
       </c>
       <c r="L22" s="3">
         <v>20300</v>
       </c>
       <c r="M22" s="3">
+        <v>20300</v>
+      </c>
+      <c r="N22" s="3">
         <v>15100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>11100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>10800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>9700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>11000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>10900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>10800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>4000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>3000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>2100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>3600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1700</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>1200</v>
       </c>
       <c r="Z22" s="3">
         <v>1200</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>3</v>
+      <c r="AA22" s="3">
+        <v>1200</v>
       </c>
       <c r="AB22" s="3" t="s">
         <v>3</v>
@@ -1861,91 +1901,97 @@
       <c r="AC22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-75500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-36200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-170300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-179500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-160700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-142700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-140600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-140200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-201300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-152300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-161000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-102100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-171100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-135000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-130200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-136200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-104100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-84200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-60700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-143800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-69400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-49200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-42100</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2027,8 +2073,11 @@
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2110,174 +2159,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-75500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-36200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-170300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-179500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-160700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-142700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-140600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-140200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-201300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-152300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-161000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-102100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-171100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-135000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-130200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-136200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-104100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-84200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-60700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-143800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-69400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-49200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-42100</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-73500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-35200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-168100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-177000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-157900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-140200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-137600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-137300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-9900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-196400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-147200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-155900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-96300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-163100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-120000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-115900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-121000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-91900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-73500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-60000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-127100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-61200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-31400</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2359,8 +2417,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2442,8 +2503,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2525,8 +2589,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2608,174 +2675,183 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-13600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-27400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-6000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-8600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-8800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-97900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>7300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-28500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-3400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-700</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V32" s="3">
         <v>2500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>3600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>7100</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y32" s="3">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z32" s="3">
         <v>1800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-500</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-73500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-35200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-168100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-177000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-157900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-140200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-137600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-137300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-9900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-196400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-147200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-155900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-96300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-163100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-120000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-115900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-121000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-91900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-73500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-60000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-127100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-61200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-31400</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2857,179 +2933,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-73500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-35200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-168100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-177000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-157900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-140200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-137600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-137300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-9900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-196400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-147200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-155900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-96300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-163100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-120000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-115900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-121000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-91900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-73500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-60000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-127100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-61200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-31400</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3059,8 +3144,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3090,77 +3176,78 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>408000</v>
+      </c>
+      <c r="E41" s="3">
         <v>475200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>375900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>505200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>302400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>407400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>376700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>483200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>470100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>371600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>393800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>180300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>378400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>471200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>356100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>367000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>540900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>757000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>363800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>414000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>293800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>373000</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3173,71 +3260,74 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>39800</v>
+      </c>
+      <c r="E42" s="3">
         <v>44500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>58900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>38100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>81400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>83900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>95200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>108700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>245600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>299700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>442900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>419300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>459200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>447900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>251000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>343700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>300000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>148100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>182200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>122100</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3256,8 +3346,11 @@
       <c r="AC42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3288,27 +3381,27 @@
       <c r="L43" s="3">
         <v>0</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N43" s="3">
+      <c r="M43" s="3">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O43" s="3">
         <v>500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>10200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>500</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R43" s="3">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S43" s="3">
         <v>8000</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3324,8 +3417,8 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y43" s="3">
-        <v>0</v>
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z43" s="3">
         <v>0</v>
@@ -3339,8 +3432,11 @@
       <c r="AC43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3422,77 +3518,80 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>168500</v>
+      </c>
+      <c r="E45" s="3">
         <v>263700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>42700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>44400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>49100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>61400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>76900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>50200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>55600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>45000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>52200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>39600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>62000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>25500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>35700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>26700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>21000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>19800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>22600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>22100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>12900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>9400</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3505,77 +3604,80 @@
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>616200</v>
+      </c>
+      <c r="E46" s="3">
         <v>783400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>477600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>587700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>432900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>552700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>548900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>642200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>771300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>716200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>888900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>639700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>909900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>945100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>642800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>745400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>861900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>925000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>568600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>558200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>306700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>382500</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3588,31 +3690,34 @@
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>117000</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3620,45 +3725,45 @@
       <c r="L47" s="3">
         <v>0</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N47" s="3">
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3">
         <v>17700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>79600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>82200</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T47" s="3">
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U47" s="3">
         <v>23200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>31100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>76800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>7500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>12500</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3671,76 +3776,79 @@
       <c r="AC47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E48" s="3">
         <v>19500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>19800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>21700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>22900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>24100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>25200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>27300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>29700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>31100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>46000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>44800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>42200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>35800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>36800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>25800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>26000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>24600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3000</v>
-      </c>
-      <c r="W48" s="3">
-        <v>1900</v>
       </c>
       <c r="X48" s="3">
         <v>1900</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
+      <c r="Y48" s="3">
+        <v>1900</v>
       </c>
       <c r="Z48" s="3" t="s">
         <v>3</v>
@@ -3754,47 +3862,50 @@
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>25100</v>
+      </c>
+      <c r="E49" s="3">
         <v>25700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>26300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>26900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>27500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>28100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>28700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>29300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>29900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>30500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>44900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>46200</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3810,8 +3921,8 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
@@ -3837,8 +3948,11 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3920,8 +4034,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4003,77 +4120,80 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E52" s="3">
         <v>20700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>22600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>18700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>20400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>20800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>20200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>29900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>31300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>35300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>33000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>33100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>49800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>30200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>23900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>16500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>17300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>17000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>26300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>9500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4600</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4086,8 +4206,11 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4169,77 +4292,80 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>794400</v>
+      </c>
+      <c r="E54" s="3">
         <v>849300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>546400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>655000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>503700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>625700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>623000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>728700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>862200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>813100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1012800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>781500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1081500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1093300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>703600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>787700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>905200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>989800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>631700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>640500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>325500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>401400</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4252,8 +4378,11 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4283,8 +4412,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4314,77 +4444,78 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E57" s="3">
         <v>4700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>10700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>11600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>11900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>12000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>22300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>10300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>8900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>9800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>12800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>13100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>8900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>10300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>16100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>12300</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4397,8 +4528,11 @@
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4426,11 +4560,11 @@
       <c r="K58" s="3">
         <v>0</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3">
-        <v>300</v>
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N58" s="3">
         <v>300</v>
@@ -4439,14 +4573,14 @@
         <v>300</v>
       </c>
       <c r="P58" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q58" s="3">
         <v>3800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1600</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4462,8 +4596,8 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
+      <c r="X58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y58" s="3">
         <v>0</v>
@@ -4480,77 +4614,80 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>116200</v>
+      </c>
+      <c r="E59" s="3">
         <v>136700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>133200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>101600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>106200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>92500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>109900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>109000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>132400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>93400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>122900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>83500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>109300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>80500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>85100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>65900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>79800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>51800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>51500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>29600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>22600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>23100</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4563,77 +4700,80 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>134400</v>
+      </c>
+      <c r="E60" s="3">
         <v>141500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>143800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>106100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>110100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>96600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>121400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>119200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>141200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>103500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>135100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>95800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>131900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>94700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>95600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>75700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>92600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>64900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>60400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>39900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>38700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>35500</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4646,77 +4786,80 @@
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1717600</v>
+      </c>
+      <c r="E61" s="3">
         <v>1715900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1726700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1721100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1718900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1713300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1707600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1698700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1693200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1708100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1705100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1376600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1375300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1362700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>477400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>471900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>466600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>461300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>91800</v>
-      </c>
-      <c r="V61" s="3">
-        <v>75000</v>
       </c>
       <c r="W61" s="3">
         <v>75000</v>
       </c>
       <c r="X61" s="3">
+        <v>75000</v>
+      </c>
+      <c r="Y61" s="3">
         <v>54900</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -4729,77 +4872,80 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>24500</v>
+      </c>
+      <c r="E62" s="3">
         <v>28800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>18300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>21600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>24200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>29400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>38900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>41200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>42900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>42300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>38300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>44900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>29900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>24000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>22600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>21700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>18500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>11500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>400</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4812,8 +4958,11 @@
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4895,8 +5044,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4978,8 +5130,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5061,77 +5216,80 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1887300</v>
+      </c>
+      <c r="E66" s="3">
         <v>1898900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1900600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1862600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1865700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1851300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1877700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1867200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1887800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1854100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1883200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1524900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1545800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1488600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>645700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>623900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>639500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>609100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>223200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>180800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>162600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>149200</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5144,8 +5302,11 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5175,8 +5336,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5258,8 +5420,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5341,8 +5506,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5404,13 +5572,13 @@
         <v>0</v>
       </c>
       <c r="W70" s="3">
-        <v>479000</v>
+        <v>0</v>
       </c>
       <c r="X70" s="3">
         <v>479000</v>
       </c>
       <c r="Y70" s="3">
-        <v>0</v>
+        <v>479000</v>
       </c>
       <c r="Z70" s="3">
         <v>0</v>
@@ -5424,8 +5592,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5507,77 +5678,80 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2669200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2595700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2560500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2392400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2215400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2057500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1918100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1780600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1643200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1633400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1437000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1289800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1133900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1037500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-888800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-768800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-652900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-531900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-440000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-366600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-319500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-230300</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5590,8 +5764,11 @@
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5673,8 +5850,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5756,8 +5936,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5839,77 +6022,80 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1092900</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1049500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1354300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-1207500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-1362000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-1225700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-1254600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-1138400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-1025500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-1041000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-870400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-743400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-464300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-395300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>57900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>163800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>265800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>380700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>408500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>459800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-316100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-226900</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5922,8 +6108,11 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6005,179 +6194,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-73500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-35200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-168100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-177000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-157900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-140200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-137600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-137300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-9900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-196400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-147200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-155900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-96300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-163100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-120000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-115900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-121000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-91900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-73500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-60000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-127100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-61200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-31400</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6207,8 +6405,9 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6228,26 +6427,26 @@
         <v>1600</v>
       </c>
       <c r="I83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J83" s="3">
         <v>1700</v>
-      </c>
-      <c r="J83" s="3">
-        <v>1600</v>
       </c>
       <c r="K83" s="3">
         <v>1600</v>
       </c>
       <c r="L83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="M83" s="3">
         <v>1900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>300</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6266,18 +6465,18 @@
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V83" s="3">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W83" s="3">
         <v>400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>100</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6290,8 +6489,11 @@
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6373,8 +6575,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6456,8 +6661,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6539,8 +6747,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6622,8 +6833,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6705,77 +6919,80 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>74700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-219500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-124800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-145200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-113400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-144300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-93200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-135200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-30500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-160600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-133900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-121600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-91700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-150800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-96300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-131700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-87800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-83900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-76200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-50000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-127400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-59100</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6788,8 +7005,11 @@
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6819,16 +7039,17 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1500</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-400</v>
       </c>
       <c r="F91" s="3">
         <v>-400</v>
@@ -6837,59 +7058,59 @@
         <v>-400</v>
       </c>
       <c r="H91" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="I91" s="3">
-        <v>-800</v>
+        <v>0</v>
       </c>
       <c r="J91" s="3">
         <v>-800</v>
       </c>
       <c r="K91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="L91" s="3">
         <v>-3900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-6500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-400</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6902,8 +7123,11 @@
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6985,8 +7209,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7068,77 +7295,80 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E94" s="3">
         <v>22800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>37700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>4100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>12300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>18000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>146900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>149700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>138600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>21800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>59000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-282100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>83000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-45100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-129000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>38000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-16900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-197300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7151,8 +7381,11 @@
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7182,8 +7415,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7265,8 +7499,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7348,8 +7585,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7431,8 +7671,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7514,77 +7757,80 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E100" s="3">
         <v>279500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>307000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>150200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>6400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-20800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>325400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-135500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>547900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>4500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>439200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>42900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>367500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-11600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7597,8 +7843,11 @@
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7680,77 +7929,80 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>72000</v>
+      </c>
+      <c r="E102" s="3">
         <v>82800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-129400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>199500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-110500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>18200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-68900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>13100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>98500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-22200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>213300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-198000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-92600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>115100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-8700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-174000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-216100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>393300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-50200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>120200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-142000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-63200</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7761,6 +8013,9 @@
         <v>3</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BBIO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BBIO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="92">
   <si>
     <t>BBIO</t>
   </si>
@@ -656,208 +656,212 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E8" s="3">
         <v>2200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>211100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>73700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>12900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>54000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>8100</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V8" s="3">
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W8" s="3">
         <v>13800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>26700</v>
       </c>
-      <c r="X8" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>0</v>
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA8" s="3">
         <v>0</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>3</v>
+      <c r="AB8" s="3">
+        <v>0</v>
       </c>
       <c r="AC8" s="3" t="s">
         <v>3</v>
@@ -865,8 +869,11 @@
       <c r="AD8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -886,32 +893,32 @@
         <v>600</v>
       </c>
       <c r="I9" s="3">
+        <v>600</v>
+      </c>
+      <c r="J9" s="3">
         <v>700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>600</v>
-      </c>
-      <c r="K9" s="3">
-        <v>700</v>
       </c>
       <c r="L9" s="3">
         <v>700</v>
       </c>
       <c r="M9" s="3">
+        <v>700</v>
+      </c>
+      <c r="N9" s="3">
         <v>1300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>100</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
@@ -927,12 +934,12 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W9" s="3">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X9" s="3">
         <v>2500</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
@@ -951,53 +958,56 @@
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E10" s="3">
         <v>1600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>210500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1000</v>
       </c>
-      <c r="I10" s="3">
-        <v>1100</v>
-      </c>
       <c r="J10" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K10" s="3">
         <v>1300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>73000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>11300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>53900</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1013,12 +1023,12 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W10" s="3">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X10" s="3">
         <v>24200</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1037,8 +1047,11 @@
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1069,94 +1082,98 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>120400</v>
+      </c>
+      <c r="E12" s="3">
         <v>114700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>141000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>130200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>125100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>107500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>92900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>90900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>92500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>108400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>107600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>122200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>104300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>102000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>122600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>90200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>92100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>86600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>68200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>57500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>55300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>95200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>42900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>51200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>31100</v>
       </c>
-      <c r="AB12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1241,44 +1258,47 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-47400</v>
+      </c>
+      <c r="E14" s="3">
         <v>-123400</v>
       </c>
-      <c r="E14" s="3">
-        <v>30000</v>
-      </c>
       <c r="F14" s="3">
-        <v>800</v>
+        <v>21900</v>
       </c>
       <c r="G14" s="3">
-        <v>300</v>
+        <v>-20500</v>
       </c>
       <c r="H14" s="3">
-        <v>3500</v>
+        <v>5600</v>
       </c>
       <c r="I14" s="3">
-        <v>3400</v>
+        <v>2100</v>
       </c>
       <c r="J14" s="3">
+        <v>3600</v>
+      </c>
+      <c r="K14" s="3">
         <v>7700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>5000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>8400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>22700</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1300,26 +1320,26 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>400</v>
-      </c>
-      <c r="X14" s="3">
-        <v>2000</v>
       </c>
       <c r="Y14" s="3">
         <v>2000</v>
       </c>
       <c r="Z14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AA14" s="3">
         <v>-19300</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>3</v>
+      <c r="AB14" s="3">
+        <v>0</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>3</v>
@@ -1327,31 +1347,34 @@
       <c r="AD14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1413,8 +1436,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1442,180 +1468,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>51400</v>
+        <v>189900</v>
       </c>
       <c r="E17" s="3">
-        <v>237400</v>
+        <v>174800</v>
       </c>
       <c r="F17" s="3">
-        <v>179200</v>
+        <v>207400</v>
       </c>
       <c r="G17" s="3">
-        <v>161800</v>
+        <v>178400</v>
       </c>
       <c r="H17" s="3">
-        <v>147700</v>
+        <v>161500</v>
       </c>
       <c r="I17" s="3">
-        <v>128000</v>
+        <v>144200</v>
       </c>
       <c r="J17" s="3">
+        <v>124600</v>
+      </c>
+      <c r="K17" s="3">
         <v>131100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>129500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>153900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>175400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>178500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>151800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>148000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>168000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>127600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>128100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>124600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>102500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>92500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>81700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>133100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>63800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>46300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>41500</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-49200</v>
+        <v>-187100</v>
       </c>
       <c r="E18" s="3">
-        <v>-26300</v>
+        <v>-172600</v>
       </c>
       <c r="F18" s="3">
-        <v>-177500</v>
+        <v>3700</v>
       </c>
       <c r="G18" s="3">
-        <v>-157700</v>
+        <v>-176700</v>
       </c>
       <c r="H18" s="3">
-        <v>-146100</v>
+        <v>-157400</v>
       </c>
       <c r="I18" s="3">
-        <v>-126200</v>
+        <v>-142600</v>
       </c>
       <c r="J18" s="3">
-        <v>-129200</v>
+        <v>-122800</v>
       </c>
       <c r="K18" s="3">
         <v>-129200</v>
       </c>
       <c r="L18" s="3">
+        <v>-129200</v>
+      </c>
+      <c r="M18" s="3">
         <v>-80200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-173700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-165600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-149500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-94000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-167500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-127500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-120000</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V18" s="3">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W18" s="3">
         <v>-78700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-55000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-133100</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z18" s="3">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-46300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-41500</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1646,136 +1679,140 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-3400</v>
+        <v>4800</v>
       </c>
       <c r="E20" s="3">
-        <v>13600</v>
+        <v>8600</v>
       </c>
       <c r="F20" s="3">
-        <v>27400</v>
+        <v>-1300</v>
       </c>
       <c r="G20" s="3">
-        <v>-1500</v>
+        <v>-500</v>
       </c>
       <c r="H20" s="3">
-        <v>6000</v>
+        <v>-100</v>
       </c>
       <c r="I20" s="3">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>300</v>
+      </c>
+      <c r="K20" s="3">
         <v>8600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>8800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>97900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-7300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>28500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>6100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>3400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>700</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V20" s="3">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W20" s="3">
         <v>-2500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z20" s="3">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>500</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-51000</v>
+        <v>-190400</v>
       </c>
       <c r="E21" s="3">
-        <v>-11100</v>
+        <v>-179600</v>
       </c>
       <c r="F21" s="3">
-        <v>-148500</v>
+        <v>6700</v>
       </c>
       <c r="G21" s="3">
-        <v>-157500</v>
+        <v>-174600</v>
       </c>
       <c r="H21" s="3">
-        <v>-138500</v>
+        <v>-155700</v>
       </c>
       <c r="I21" s="3">
-        <v>-121000</v>
+        <v>-140900</v>
       </c>
       <c r="J21" s="3">
+        <v>-121500</v>
+      </c>
+      <c r="K21" s="3">
         <v>-118900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-118700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>19300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-179100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-135600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-149700</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1794,15 +1831,15 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X21" s="3">
         <v>-58200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-139900</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1818,85 +1855,88 @@
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E22" s="3">
         <v>22900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>23500</v>
-      </c>
-      <c r="F22" s="3">
-        <v>20300</v>
       </c>
       <c r="G22" s="3">
         <v>20300</v>
       </c>
       <c r="H22" s="3">
+        <v>20300</v>
+      </c>
+      <c r="I22" s="3">
         <v>20600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>20100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>20000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>19800</v>
-      </c>
-      <c r="L22" s="3">
-        <v>20300</v>
       </c>
       <c r="M22" s="3">
         <v>20300</v>
       </c>
       <c r="N22" s="3">
+        <v>20300</v>
+      </c>
+      <c r="O22" s="3">
         <v>15100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>11100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>10800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>9700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>11000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>10900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>10800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>4000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>3000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>2100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>3600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>1700</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>1200</v>
       </c>
       <c r="AA22" s="3">
         <v>1200</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>3</v>
+      <c r="AB22" s="3">
+        <v>1200</v>
       </c>
       <c r="AC22" s="3" t="s">
         <v>3</v>
@@ -1904,117 +1944,123 @@
       <c r="AD22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-164300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-75500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-36200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-170300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-179500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-160700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-142700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-140600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-140200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-201300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-152300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-161000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-102100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-171100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-135000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-130200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-136200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-104100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-84200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-60700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-143800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-69400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-49200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-42100</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -2076,8 +2122,11 @@
       <c r="AD24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2162,180 +2211,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-164300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-75500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-36200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-170300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-179500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-160700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-142700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-140600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-140200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-201300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-152300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-161000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-102100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-171100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-135000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-130200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-136200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-104100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-84200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-60700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-143800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-69400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-49200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-42100</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-162000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-73500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-35200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-168100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-177000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-157900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-140200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-137600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-137300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-9900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-196400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-147200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-155900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-96300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-163100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-120000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-115900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-121000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-91900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-73500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-60000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-127100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-61200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-31400</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2420,8 +2478,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2506,8 +2567,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2592,8 +2656,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2678,180 +2745,189 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>3400</v>
+        <v>-4800</v>
       </c>
       <c r="E32" s="3">
-        <v>-13600</v>
+        <v>-8600</v>
       </c>
       <c r="F32" s="3">
-        <v>-27400</v>
+        <v>1300</v>
       </c>
       <c r="G32" s="3">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="H32" s="3">
-        <v>-6000</v>
+        <v>100</v>
       </c>
       <c r="I32" s="3">
-        <v>-3600</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K32" s="3">
         <v>-8600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-8800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-97900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>7300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-28500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-6100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-3400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-700</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V32" s="3">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W32" s="3">
         <v>2500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>7100</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z32" s="3">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA32" s="3">
         <v>1800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-500</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-162000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-73500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-35200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-168100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-177000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-157900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-140200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-137600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-137300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-9900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-196400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-147200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-155900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-96300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-163100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-120000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-115900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-121000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-91900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-73500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-60000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-127100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-61200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-31400</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2936,185 +3012,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-162000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-73500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-35200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-168100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-177000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-157900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-140200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-137600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-137300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-9900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-196400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-147200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-155900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-96300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-163100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-120000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-115900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-121000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-91900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-73500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-60000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-127100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-61200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-31400</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3145,8 +3230,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3177,80 +3263,81 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>266300</v>
+      </c>
+      <c r="E41" s="3">
         <v>408000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>475200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>375900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>505200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>302400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>407400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>376700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>483200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>470100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>371600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>393800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>180300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>378400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>471200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>356100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>367000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>540900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>757000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>363800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>414000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>293800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>373000</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3263,74 +3350,77 @@
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>39800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>44500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>58900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>38100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>81400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>83900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>95200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>108700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>245600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>299700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>442900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>419300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>459200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>447900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>251000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>343700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>300000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>148100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>182200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>122100</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3349,31 +3439,34 @@
       <c r="AD42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>2600</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>235500</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
+        <v>5200</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
+        <v>8600</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3384,27 +3477,27 @@
       <c r="M43" s="3">
         <v>0</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O43" s="3">
+      <c r="N43" s="3">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3">
         <v>500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>10200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>500</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S43" s="3">
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T43" s="3">
         <v>8000</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3420,8 +3513,8 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z43" s="3">
-        <v>0</v>
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA43" s="3">
         <v>0</v>
@@ -3435,31 +3528,34 @@
       <c r="AD43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3521,80 +3617,83 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>168500</v>
-      </c>
-      <c r="E45" s="3">
-        <v>263700</v>
-      </c>
-      <c r="F45" s="3">
-        <v>42700</v>
+        <v>7400</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G45" s="3">
-        <v>44400</v>
-      </c>
-      <c r="H45" s="3">
-        <v>49100</v>
-      </c>
-      <c r="I45" s="3">
-        <v>61400</v>
-      </c>
-      <c r="J45" s="3">
+        <v>11000</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>76900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>50200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>55600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>45000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>52200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>39600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>62000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>25500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>35700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>26700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>21000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>19800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>22600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>22100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>12900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>9400</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3607,80 +3706,83 @@
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>444600</v>
+      </c>
+      <c r="E46" s="3">
         <v>616200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>783400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>477600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>587700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>432900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>552700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>548900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>642200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>771300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>716200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>888900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>639700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>909900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>945100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>642800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>745400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>861900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>925000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>568600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>558200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>306700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>382500</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3693,34 +3795,37 @@
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>160400</v>
+      </c>
+      <c r="E47" s="3">
         <v>117000</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
+      <c r="H47" s="3">
+        <v>500</v>
+      </c>
+      <c r="I47" s="3">
+        <v>800</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3728,45 +3833,45 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O47" s="3">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3">
         <v>17700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>79600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>82200</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U47" s="3">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V47" s="3">
         <v>23200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>31100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>76800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>7500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>12500</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3779,79 +3884,82 @@
       <c r="AD47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E48" s="3">
         <v>17100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>19500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>19800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>22900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>24100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>25200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>27300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>29700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>31100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>46000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>44800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>42200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>35800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>36800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>25800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>26000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>24600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3000</v>
-      </c>
-      <c r="X48" s="3">
-        <v>1900</v>
       </c>
       <c r="Y48" s="3">
         <v>1900</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>3</v>
+      <c r="Z48" s="3">
+        <v>1900</v>
       </c>
       <c r="AA48" s="3" t="s">
         <v>3</v>
@@ -3865,50 +3973,53 @@
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>24500</v>
+      </c>
+      <c r="E49" s="3">
         <v>25100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>25700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>26300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>26900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>27500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>28100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>28700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>29300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>29900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>30500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>44900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>46200</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3924,8 +4035,8 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V49" s="3">
-        <v>0</v>
+      <c r="V49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W49" s="3">
         <v>0</v>
@@ -3951,8 +4062,11 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4037,8 +4151,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4123,80 +4240,83 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E52" s="3">
         <v>18900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>20700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>22600</v>
       </c>
-      <c r="G52" s="3">
-        <v>18700</v>
-      </c>
       <c r="H52" s="3">
-        <v>20400</v>
+        <v>18200</v>
       </c>
       <c r="I52" s="3">
+        <v>19600</v>
+      </c>
+      <c r="J52" s="3">
         <v>20800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>20200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>29900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>31300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>35300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>33000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>33100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>49800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>30200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>23900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>16500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>17300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>17000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>26300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>9500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>4600</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4209,8 +4329,11 @@
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4295,80 +4418,83 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>665000</v>
+      </c>
+      <c r="E54" s="3">
         <v>794400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>849300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>546400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>655000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>503700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>625700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>623000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>728700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>862200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>813100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1012800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>781500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1081500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1093300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>703600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>787700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>905200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>989800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>631700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>640500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>325500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>401400</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4381,8 +4507,11 @@
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4413,8 +4542,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4445,80 +4575,81 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E57" s="3">
         <v>18100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>10700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>11600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>11900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>12000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>22300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>10300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>8900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>9800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>12800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>13100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>8900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>10300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>16100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>12300</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4531,31 +4662,34 @@
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>4600</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>4600</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>4100</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>4100</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -4563,11 +4697,11 @@
       <c r="L58" s="3">
         <v>0</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N58" s="3">
-        <v>300</v>
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O58" s="3">
         <v>300</v>
@@ -4576,14 +4710,14 @@
         <v>300</v>
       </c>
       <c r="Q58" s="3">
+        <v>300</v>
+      </c>
+      <c r="R58" s="3">
         <v>3800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1600</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4599,8 +4733,8 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z58" s="3">
         <v>0</v>
@@ -4617,80 +4751,83 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>116200</v>
+        <v>16600</v>
       </c>
       <c r="E59" s="3">
-        <v>136700</v>
+        <v>21500</v>
       </c>
       <c r="F59" s="3">
-        <v>133200</v>
+        <v>22700</v>
       </c>
       <c r="G59" s="3">
-        <v>101600</v>
+        <v>12100</v>
       </c>
       <c r="H59" s="3">
-        <v>106200</v>
+        <v>12600</v>
       </c>
       <c r="I59" s="3">
-        <v>92500</v>
+        <v>16800</v>
       </c>
       <c r="J59" s="3">
+        <v>9200</v>
+      </c>
+      <c r="K59" s="3">
         <v>109900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>109000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>132400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>93400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>122900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>83500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>109300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>80500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>85100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>65900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>79800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>51800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>51500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>29600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>22600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>23100</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4703,80 +4840,83 @@
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>139200</v>
+      </c>
+      <c r="E60" s="3">
         <v>134400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>141500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>143800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>106100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>110100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>96600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>121400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>119200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>141200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>103500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>135100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>95800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>131900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>94700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>95600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>75700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>92600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>64900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>60400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>39900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>38700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>35500</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4789,80 +4929,83 @@
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1717600</v>
+        <v>1725100</v>
       </c>
       <c r="E61" s="3">
-        <v>1715900</v>
+        <v>1724700</v>
       </c>
       <c r="F61" s="3">
-        <v>1726700</v>
+        <v>1724200</v>
       </c>
       <c r="G61" s="3">
-        <v>1721100</v>
+        <v>1735700</v>
       </c>
       <c r="H61" s="3">
-        <v>1718900</v>
+        <v>1730900</v>
       </c>
       <c r="I61" s="3">
-        <v>1713300</v>
+        <v>1729900</v>
       </c>
       <c r="J61" s="3">
+        <v>1725200</v>
+      </c>
+      <c r="K61" s="3">
         <v>1707600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1698700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1693200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1708100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1705100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1376600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1375300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1362700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>477400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>471900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>466600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>461300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>91800</v>
-      </c>
-      <c r="W61" s="3">
-        <v>75000</v>
       </c>
       <c r="X61" s="3">
         <v>75000</v>
       </c>
       <c r="Y61" s="3">
+        <v>75000</v>
+      </c>
+      <c r="Z61" s="3">
         <v>54900</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
@@ -4875,80 +5018,83 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>24500</v>
+        <v>400</v>
       </c>
       <c r="E62" s="3">
-        <v>28800</v>
+        <v>500</v>
       </c>
       <c r="F62" s="3">
-        <v>18300</v>
+        <v>600</v>
       </c>
       <c r="G62" s="3">
-        <v>21600</v>
+        <v>5600</v>
       </c>
       <c r="H62" s="3">
-        <v>24200</v>
+        <v>7600</v>
       </c>
       <c r="I62" s="3">
-        <v>29400</v>
+        <v>7400</v>
       </c>
       <c r="J62" s="3">
+        <v>10600</v>
+      </c>
+      <c r="K62" s="3">
         <v>38900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>41200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>42900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>42300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>38300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>44900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>29900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>24000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>22600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>21700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>18500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>11500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>400</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4961,8 +5107,11 @@
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5047,8 +5196,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5133,8 +5285,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5219,80 +5374,83 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1887300</v>
+        <v>1883400</v>
       </c>
       <c r="E66" s="3">
-        <v>1898900</v>
+        <v>1876500</v>
       </c>
       <c r="F66" s="3">
-        <v>1900600</v>
+        <v>1886200</v>
       </c>
       <c r="G66" s="3">
-        <v>1862600</v>
+        <v>1888900</v>
       </c>
       <c r="H66" s="3">
-        <v>1865700</v>
+        <v>1848700</v>
       </c>
       <c r="I66" s="3">
-        <v>1851300</v>
+        <v>1853300</v>
       </c>
       <c r="J66" s="3">
+        <v>1839300</v>
+      </c>
+      <c r="K66" s="3">
         <v>1877700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1867200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1887800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1854100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1883200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1524900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1545800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1488600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>645700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>623900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>639500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>609100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>223200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>180800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>162600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>149200</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5305,8 +5463,11 @@
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5337,8 +5498,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5423,8 +5585,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5509,8 +5674,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5575,13 +5743,13 @@
         <v>0</v>
       </c>
       <c r="X70" s="3">
-        <v>479000</v>
+        <v>0</v>
       </c>
       <c r="Y70" s="3">
         <v>479000</v>
       </c>
       <c r="Z70" s="3">
-        <v>0</v>
+        <v>479000</v>
       </c>
       <c r="AA70" s="3">
         <v>0</v>
@@ -5595,8 +5763,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5681,80 +5852,83 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2831200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2669200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2595700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2560500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2392400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2215400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2057500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1918100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1780600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1643200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1633400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1437000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1289800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1133900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1037500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-888800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-768800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-652900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-531900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-440000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-366600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-319500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-230300</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5767,8 +5941,11 @@
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5853,8 +6030,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5939,8 +6119,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6025,80 +6208,83 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1229900</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1092900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1049500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-1354300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-1207500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-1362000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-1225700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-1254600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-1138400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-1025500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-1041000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-870400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-743400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-464300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-395300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>57900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>163800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>265800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>380700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>408500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>459800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-316100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-226900</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6111,8 +6297,11 @@
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6197,185 +6386,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-162000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-73500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-35200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-168100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-177000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-157900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-140200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-137600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-137300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-9900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-196400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-147200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-155900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-96300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-163100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-120000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-115900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-121000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-91900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-73500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-60000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-127100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-61200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-31400</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6406,50 +6604,51 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1600</v>
+        <v>1000</v>
       </c>
       <c r="E83" s="3">
-        <v>1600</v>
+        <v>1000</v>
       </c>
       <c r="F83" s="3">
-        <v>1600</v>
+        <v>1000</v>
       </c>
       <c r="G83" s="3">
-        <v>1600</v>
+        <v>1100</v>
       </c>
       <c r="H83" s="3">
-        <v>1600</v>
+        <v>1000</v>
       </c>
       <c r="I83" s="3">
-        <v>1600</v>
+        <v>1300</v>
       </c>
       <c r="J83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K83" s="3">
         <v>1700</v>
-      </c>
-      <c r="K83" s="3">
-        <v>1600</v>
       </c>
       <c r="L83" s="3">
         <v>1600</v>
       </c>
       <c r="M83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="N83" s="3">
         <v>1900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>300</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6468,18 +6667,18 @@
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W83" s="3">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X83" s="3">
         <v>400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>100</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6492,8 +6691,11 @@
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6578,8 +6780,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6664,8 +6869,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6750,8 +6958,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6836,8 +7047,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6922,80 +7136,83 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-180600</v>
+      </c>
+      <c r="E89" s="3">
         <v>74700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-219500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-124800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-145200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-113400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-144300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-93200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-135200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-30500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-160600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-133900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-121600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-91700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-150800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-96300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-131700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-87800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-83900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-76200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-50000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-127400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-59100</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7008,8 +7225,11 @@
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7040,19 +7260,20 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-2400</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
-        <v>-1500</v>
+        <v>-100</v>
       </c>
       <c r="F91" s="3">
-        <v>-400</v>
+        <v>-700</v>
       </c>
       <c r="G91" s="3">
         <v>-400</v>
@@ -7061,59 +7282,59 @@
         <v>-400</v>
       </c>
       <c r="I91" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="J91" s="3">
-        <v>-800</v>
+        <v>0</v>
       </c>
       <c r="K91" s="3">
         <v>-800</v>
       </c>
       <c r="L91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="M91" s="3">
         <v>-3900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-6500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-400</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
@@ -7126,8 +7347,11 @@
       <c r="AD91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7212,8 +7436,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7298,80 +7525,83 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>38200</v>
+      </c>
+      <c r="E94" s="3">
         <v>3000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>22800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>37700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>4100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>12300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>18000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>146900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>149700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>138600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>21800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>59000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-282100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>83000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-45100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-129000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>38000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-16900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-197300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7384,8 +7614,11 @@
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7416,31 +7649,32 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -7502,8 +7736,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7588,8 +7825,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7674,8 +7914,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7760,80 +8003,83 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-5700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>279500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>307000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>150200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>6400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-20800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>325400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-135500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>547900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>4500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>439200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>42900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>367500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-11600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7846,31 +8092,34 @@
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -7932,80 +8181,83 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-141600</v>
+      </c>
+      <c r="E102" s="3">
         <v>72000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>82800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-129400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>199500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-110500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>18200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-68900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>13100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>98500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-22200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>213300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-198000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-92600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>115100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-8700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-174000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-216100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>393300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-50200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>120200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-142000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-63200</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
@@ -8016,6 +8268,9 @@
         <v>3</v>
       </c>
       <c r="AD102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BBIO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BBIO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="92">
   <si>
     <t>BBIO</t>
   </si>
@@ -656,215 +656,218 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AE7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E8" s="3">
         <v>2700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>211100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>73700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>12900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>54000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8100</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W8" s="3">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X8" s="3">
         <v>13800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>26700</v>
       </c>
-      <c r="Y8" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA8" s="3">
-        <v>0</v>
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB8" s="3">
         <v>0</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>3</v>
+      <c r="AC8" s="3">
+        <v>0</v>
       </c>
       <c r="AD8" s="3" t="s">
         <v>3</v>
@@ -872,13 +875,16 @@
       <c r="AE8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>600</v>
+        <v>2100</v>
       </c>
       <c r="E9" s="3">
         <v>600</v>
@@ -896,32 +902,32 @@
         <v>600</v>
       </c>
       <c r="J9" s="3">
+        <v>600</v>
+      </c>
+      <c r="K9" s="3">
         <v>700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>600</v>
-      </c>
-      <c r="L9" s="3">
-        <v>700</v>
       </c>
       <c r="M9" s="3">
         <v>700</v>
       </c>
       <c r="N9" s="3">
+        <v>700</v>
+      </c>
+      <c r="O9" s="3">
         <v>1300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>100</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
@@ -937,12 +943,12 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X9" s="3">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y9" s="3">
         <v>2500</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
@@ -961,56 +967,59 @@
       <c r="AE9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E10" s="3">
         <v>2100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>210500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>73000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>11300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>53900</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1026,12 +1035,12 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X10" s="3">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y10" s="3">
         <v>24200</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1050,8 +1059,11 @@
       <c r="AE10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1083,97 +1095,101 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>130400</v>
+      </c>
+      <c r="E12" s="3">
         <v>120400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>114700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>141000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>130200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>125100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>107500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>92900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>90900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>92500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>108400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>107600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>122200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>104300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>102000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>122600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>90200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>92100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>86600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>68200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>57500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>55300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>95200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>42900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>51200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>31100</v>
       </c>
-      <c r="AC12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1261,47 +1277,50 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E14" s="3">
         <v>-47400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-123400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>21900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-20500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>5600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>7700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>5000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>8400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>22700</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1323,26 +1342,26 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>400</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>2000</v>
       </c>
       <c r="Z14" s="3">
         <v>2000</v>
       </c>
       <c r="AA14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AB14" s="3">
         <v>-19300</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>3</v>
+      <c r="AC14" s="3">
+        <v>0</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>3</v>
@@ -1350,16 +1369,19 @@
       <c r="AE14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E15" s="3">
         <v>1500</v>
-      </c>
-      <c r="E15" s="3">
-        <v>1600</v>
       </c>
       <c r="F15" s="3">
         <v>1600</v>
@@ -1377,7 +1399,7 @@
         <v>1600</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1439,8 +1461,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1469,186 +1494,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>227200</v>
+      </c>
+      <c r="E17" s="3">
         <v>189900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>174800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>207400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>178400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>161500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>144200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>124600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>131100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>129500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>153900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>175400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>178500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>151800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>148000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>168000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>127600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>128100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>124600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>102500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>92500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>81700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>133100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>63800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>46300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>41500</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-221300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-187100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-172600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-176700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-157400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-142600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-122800</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-129200</v>
       </c>
       <c r="L18" s="3">
         <v>-129200</v>
       </c>
       <c r="M18" s="3">
+        <v>-129200</v>
+      </c>
+      <c r="N18" s="3">
         <v>-80200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-173700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-165600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-149500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-94000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-167500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-127500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-120000</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X18" s="3">
         <v>-78700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-55000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-133100</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA18" s="3">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB18" s="3">
         <v>-46300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-41500</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1680,142 +1712,146 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E20" s="3">
         <v>4800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>8600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>8600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>8800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>97900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-7300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>28500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>6100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>3400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>700</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X20" s="3">
         <v>-2500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-7100</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA20" s="3">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>500</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-235000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-190400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-179600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>6700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-174600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-155700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-140900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-121500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-118900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-118700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>19300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-179100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-135600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-149700</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1834,15 +1870,15 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="3">
         <v>-58200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-139900</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1858,88 +1894,91 @@
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>29800</v>
+      </c>
+      <c r="E22" s="3">
         <v>23100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>22900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>23500</v>
-      </c>
-      <c r="G22" s="3">
-        <v>20300</v>
       </c>
       <c r="H22" s="3">
         <v>20300</v>
       </c>
       <c r="I22" s="3">
+        <v>20300</v>
+      </c>
+      <c r="J22" s="3">
         <v>20600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>20100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>20000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>19800</v>
-      </c>
-      <c r="M22" s="3">
-        <v>20300</v>
       </c>
       <c r="N22" s="3">
         <v>20300</v>
       </c>
       <c r="O22" s="3">
+        <v>20300</v>
+      </c>
+      <c r="P22" s="3">
         <v>15100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>11100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>10800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>9700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>11000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>10900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>10800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>4000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>3000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>2100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>3600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>1700</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>1200</v>
       </c>
       <c r="AB22" s="3">
         <v>1200</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>3</v>
+      <c r="AC22" s="3">
+        <v>1200</v>
       </c>
       <c r="AD22" s="3" t="s">
         <v>3</v>
@@ -1947,102 +1986,108 @@
       <c r="AE22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-266200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-164300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-75500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-36200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-170300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-179500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-160700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-142700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-140600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-140200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-201300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-152300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-161000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-102100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-171100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-135000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-130200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-136200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-104100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-84200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-60700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-143800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-69400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-49200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-42100</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
+      <c r="D24" s="3">
+        <v>1200</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>3</v>
@@ -2062,8 +2107,8 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -2125,8 +2170,11 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2214,186 +2262,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-267400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-164300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-75500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-36200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-170300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-179500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-160700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-142700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-140600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-140200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-201300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-152300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-161000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-102100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-171100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-135000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-130200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-136200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-104100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-84200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-60700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-143800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-69400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-49200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-42100</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-265100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-162000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-73500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-35200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-168100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-177000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-157900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-140200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-137600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-137300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-9900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-196400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-147200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-155900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-96300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-163100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-120000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-115900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-121000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-91900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-73500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-60000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-127100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-61200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-31400</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2481,8 +2538,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2570,8 +2630,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2659,8 +2722,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2748,186 +2814,195 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-8600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-8600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-8800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-97900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>7300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-28500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-6100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-3400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-700</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X32" s="3">
         <v>2500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>7100</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA32" s="3">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB32" s="3">
         <v>1800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-500</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-265100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-162000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-73500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-35200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-168100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-177000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-157900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-140200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-137600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-137300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-9900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-196400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-147200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-155900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-96300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-163100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-120000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-115900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-121000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-91900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-73500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-60000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-127100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-61200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-31400</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3015,191 +3090,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-265100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-162000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-73500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-35200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-168100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-177000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-157900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-140200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-137600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-137300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-9900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-196400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-147200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-155900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-96300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-163100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-120000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-115900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-121000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-91900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-73500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-60000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-127100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-61200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-31400</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AE38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3231,8 +3315,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3264,83 +3349,84 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>681100</v>
+      </c>
+      <c r="E41" s="3">
         <v>266300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>408000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>475200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>375900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>505200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>302400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>407400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>376700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>483200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>470100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>371600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>393800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>180300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>378400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>471200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>356100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>367000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>540900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>757000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>363800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>414000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>293800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>373000</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3353,8 +3439,11 @@
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3362,68 +3451,68 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>39800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>44500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>58900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>38100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>81400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>83900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>95200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>108700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>245600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>299700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>442900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>419300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>459200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>447900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>251000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>343700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>300000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>148100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>182200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>122100</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3442,35 +3531,38 @@
       <c r="AE42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2600</v>
+        <v>4700</v>
       </c>
       <c r="E43" s="3">
+        <v>500</v>
+      </c>
+      <c r="F43" s="3">
         <v>700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>235500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>10800</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
       <c r="L43" s="3">
         <v>0</v>
       </c>
@@ -3480,27 +3572,27 @@
       <c r="N43" s="3">
         <v>0</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P43" s="3">
+      <c r="O43" s="3">
+        <v>0</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3">
         <v>500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>10200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>500</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T43" s="3">
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U43" s="3">
         <v>8000</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3516,8 +3608,8 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA43" s="3">
-        <v>0</v>
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB43" s="3">
         <v>0</v>
@@ -3531,8 +3623,11 @@
       <c r="AE43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3557,8 +3652,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3620,22 +3715,25 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>7400</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
+        <v>3700</v>
+      </c>
+      <c r="E45" s="3">
+        <v>9500</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G45" s="3">
-        <v>11000</v>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
@@ -3646,57 +3744,57 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>76900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>50200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>55600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>45000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>52200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>39600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>62000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>25500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>35700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>26700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>21000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>19800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>22600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>22100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>12900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>9400</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3709,83 +3807,86 @@
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>720700</v>
+      </c>
+      <c r="E46" s="3">
         <v>444600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>616200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>783400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>477600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>587700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>432900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>552700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>548900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>642200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>771300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>716200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>888900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>639700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>909900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>945100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>642800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>745400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>861900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>925000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>568600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>558200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>306700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>382500</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3798,37 +3899,40 @@
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>143700</v>
+      </c>
+      <c r="E47" s="3">
         <v>160400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>117000</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H47" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I47" s="3">
         <v>500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>800</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3836,45 +3940,45 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P47" s="3">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3">
         <v>17700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>79600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>82200</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V47" s="3">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W47" s="3">
         <v>23200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>31100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>76800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>7500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>12500</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3887,82 +3991,85 @@
       <c r="AE47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E48" s="3">
         <v>15100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>17100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>19500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>19800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>21700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>22900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>24100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>25200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>27300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>29700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>31100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>46000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>44800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>42200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>35800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>36800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>25800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>26000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>24600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3000</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>1900</v>
       </c>
       <c r="Z48" s="3">
         <v>1900</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>3</v>
+      <c r="AA48" s="3">
+        <v>1900</v>
       </c>
       <c r="AB48" s="3" t="s">
         <v>3</v>
@@ -3976,53 +4083,56 @@
       <c r="AE48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>23900</v>
+      </c>
+      <c r="E49" s="3">
         <v>24500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>25100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>25700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>26300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>26900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>27500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>28100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>28700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>29300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>29900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>30500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>44900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>46200</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4038,8 +4148,8 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W49" s="3">
-        <v>0</v>
+      <c r="W49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X49" s="3">
         <v>0</v>
@@ -4065,8 +4175,11 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4154,8 +4267,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4243,83 +4359,86 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E52" s="3">
         <v>20300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>18900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>20700</v>
       </c>
-      <c r="G52" s="3">
-        <v>22600</v>
-      </c>
       <c r="H52" s="3">
+        <v>21000</v>
+      </c>
+      <c r="I52" s="3">
         <v>18200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>19600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>20800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>20200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>29900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>31300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>35300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>33000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>33100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>49800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>30200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>23900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>16500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>17300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>17000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>26300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>9500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>4600</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4332,8 +4451,11 @@
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4421,83 +4543,86 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>919300</v>
+      </c>
+      <c r="E54" s="3">
         <v>665000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>794400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>849300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>546400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>655000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>503700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>625700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>623000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>728700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>862200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>813100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1012800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>781500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1081500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1093300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>703600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>787700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>905200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>989800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>631700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>640500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>325500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>401400</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4510,8 +4635,11 @@
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4543,8 +4671,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4576,83 +4705,84 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E57" s="3">
         <v>13400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>18100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>10700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>11900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>12000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>22300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>10300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>8900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>9800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>12800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>13100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>8900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>10300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>16100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>12300</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4665,46 +4795,49 @@
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>4600</v>
+        <v>4500</v>
       </c>
       <c r="E58" s="3">
         <v>4600</v>
       </c>
       <c r="F58" s="3">
+        <v>4600</v>
+      </c>
+      <c r="G58" s="3">
         <v>4500</v>
-      </c>
-      <c r="G58" s="3">
-        <v>4100</v>
       </c>
       <c r="H58" s="3">
         <v>4100</v>
       </c>
       <c r="I58" s="3">
+        <v>4100</v>
+      </c>
+      <c r="J58" s="3">
         <v>3800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3700</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O58" s="3">
-        <v>300</v>
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P58" s="3">
         <v>300</v>
@@ -4713,14 +4846,14 @@
         <v>300</v>
       </c>
       <c r="R58" s="3">
+        <v>300</v>
+      </c>
+      <c r="S58" s="3">
         <v>3800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1600</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4736,8 +4869,8 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z58" s="3">
-        <v>0</v>
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA58" s="3">
         <v>0</v>
@@ -4754,83 +4887,86 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E59" s="3">
         <v>16600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>21500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>22700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>12100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>12600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>16800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>109900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>109000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>132400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>93400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>122900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>83500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>109300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>80500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>85100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>65900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>79800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>51800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>51500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>29600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>22600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>23100</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4843,83 +4979,86 @@
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>154400</v>
+      </c>
+      <c r="E60" s="3">
         <v>139200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>134400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>141500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>143800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>106100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>110100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>96600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>121400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>119200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>141200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>103500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>135100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>95800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>131900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>94700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>95600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>75700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>92600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>64900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>60400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>39900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>38700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>35500</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4932,83 +5071,86 @@
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1726100</v>
+      </c>
+      <c r="E61" s="3">
         <v>1725100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1724700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1724200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1735700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1730900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1729900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1725200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1707600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1698700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1693200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1708100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1705100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1376600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1375300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1362700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>477400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>471900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>466600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>461300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>91800</v>
-      </c>
-      <c r="X61" s="3">
-        <v>75000</v>
       </c>
       <c r="Y61" s="3">
         <v>75000</v>
       </c>
       <c r="Z61" s="3">
+        <v>75000</v>
+      </c>
+      <c r="AA61" s="3">
         <v>54900</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
       <c r="AB61" s="3">
         <v>0</v>
       </c>
@@ -5021,83 +5163,86 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>479400</v>
+      </c>
+      <c r="E62" s="3">
         <v>400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>7400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>10600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>38900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>41200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>42900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>42300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>38300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>44900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>29900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>24000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>22600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>21700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>18500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>11500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>400</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5110,8 +5255,11 @@
       <c r="AE62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5199,8 +5347,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5288,8 +5439,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5377,83 +5531,86 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2377000</v>
+      </c>
+      <c r="E66" s="3">
         <v>1883400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1876500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1886200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1888900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1848700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1853300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1839300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1877700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1867200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1887800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1854100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1883200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1524900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1545800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1488600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>645700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>623900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>639500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>609100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>223200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>180800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>162600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>149200</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5466,8 +5623,11 @@
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5499,8 +5659,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5588,8 +5749,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5677,8 +5841,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5746,13 +5913,13 @@
         <v>0</v>
       </c>
       <c r="Y70" s="3">
-        <v>479000</v>
+        <v>0</v>
       </c>
       <c r="Z70" s="3">
         <v>479000</v>
       </c>
       <c r="AA70" s="3">
-        <v>0</v>
+        <v>479000</v>
       </c>
       <c r="AB70" s="3">
         <v>0</v>
@@ -5766,8 +5933,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5855,83 +6025,86 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-3096300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2831200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2669200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2595700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2560500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2392400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2215400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2057500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1918100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1780600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1643200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1633400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1437000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1289800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1133900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1037500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-888800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-768800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-652900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-531900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-440000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-366600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-319500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-230300</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5944,8 +6117,11 @@
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6033,8 +6209,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6122,8 +6301,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6211,83 +6393,86 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1467900</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1229900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1092900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-1049500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-1354300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-1207500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-1362000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-1225700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-1254600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-1138400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-1025500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-1041000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-870400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-743400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-464300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-395300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>57900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>163800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>265800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>380700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>408500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>459800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-316100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-226900</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6300,8 +6485,11 @@
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6389,191 +6577,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AE80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-265100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-162000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-73500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-35200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-168100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-177000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-157900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-140200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-137600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-137300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-9900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-196400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-147200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-155900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-96300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-163100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-120000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-115900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-121000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-91900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-73500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-60000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-127100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-61200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-31400</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6605,8 +6802,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6620,38 +6818,38 @@
         <v>1000</v>
       </c>
       <c r="G83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H83" s="3">
         <v>1100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1700</v>
-      </c>
-      <c r="L83" s="3">
-        <v>1600</v>
       </c>
       <c r="M83" s="3">
         <v>1600</v>
       </c>
       <c r="N83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="O83" s="3">
         <v>1900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>300</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6670,18 +6868,18 @@
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X83" s="3">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y83" s="3">
         <v>400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>100</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6694,8 +6892,11 @@
       <c r="AE83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6783,8 +6984,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6872,8 +7076,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6961,8 +7168,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7050,8 +7260,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7139,83 +7352,86 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-195300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-180600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>74700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-219500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-124800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-145200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-113400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-144300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-93200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-135200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-30500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-160600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-133900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-121600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-91700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-150800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-96300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-131700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-87800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-83900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-76200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-50000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-127400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-59100</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7228,8 +7444,11 @@
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7261,22 +7480,23 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E91" s="3">
         <v>-100</v>
       </c>
       <c r="F91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G91" s="3">
         <v>-700</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-400</v>
       </c>
       <c r="H91" s="3">
         <v>-400</v>
@@ -7285,59 +7505,59 @@
         <v>-400</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="K91" s="3">
-        <v>-800</v>
+        <v>0</v>
       </c>
       <c r="L91" s="3">
         <v>-800</v>
       </c>
       <c r="M91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="N91" s="3">
         <v>-3900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-400</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
@@ -7350,8 +7570,11 @@
       <c r="AE91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7439,8 +7662,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7528,83 +7754,86 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E94" s="3">
         <v>38200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>3000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>22800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>37700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>4100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>12300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>18000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>146900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>149700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>138600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>21800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>59000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-282100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>83000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-45100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-129000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>38000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-16900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-197300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7617,8 +7846,11 @@
       <c r="AE94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7650,8 +7882,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7676,8 +7909,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -7739,8 +7972,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7828,8 +8064,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7917,8 +8156,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8006,83 +8248,86 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>473900</v>
+      </c>
+      <c r="E100" s="3">
         <v>700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-5700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>279500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>307000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>150200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>6400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-20800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>325400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-135500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>547900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>4500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>439200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>42900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>367500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-11600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
@@ -8095,8 +8340,11 @@
       <c r="AE100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8121,8 +8369,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -8184,83 +8432,86 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>275400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-141600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>72000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>82800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-129400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>199500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-110500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>18200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-68900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>13100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>98500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-22200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>213300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-198000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-92600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>115100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-8700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-174000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-216100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>393300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-50200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>120200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-142000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-63200</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
@@ -8271,6 +8522,9 @@
         <v>3</v>
       </c>
       <c r="AE102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BBIO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BBIO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="92">
   <si>
     <t>BBIO</t>
   </si>
@@ -656,221 +656,225 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AF7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>116600</v>
+      </c>
+      <c r="E8" s="3">
         <v>5900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>211100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>73700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>12900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>54000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8100</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X8" s="3">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y8" s="3">
         <v>13800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>26700</v>
       </c>
-      <c r="Z8" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB8" s="3">
-        <v>0</v>
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC8" s="3">
         <v>0</v>
       </c>
-      <c r="AD8" s="3" t="s">
-        <v>3</v>
+      <c r="AD8" s="3">
+        <v>0</v>
       </c>
       <c r="AE8" s="3" t="s">
         <v>3</v>
@@ -878,16 +882,19 @@
       <c r="AF8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E9" s="3">
         <v>2100</v>
-      </c>
-      <c r="E9" s="3">
-        <v>600</v>
       </c>
       <c r="F9" s="3">
         <v>600</v>
@@ -905,32 +912,32 @@
         <v>600</v>
       </c>
       <c r="K9" s="3">
+        <v>600</v>
+      </c>
+      <c r="L9" s="3">
         <v>700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>600</v>
-      </c>
-      <c r="M9" s="3">
-        <v>700</v>
       </c>
       <c r="N9" s="3">
         <v>700</v>
       </c>
       <c r="O9" s="3">
+        <v>700</v>
+      </c>
+      <c r="P9" s="3">
         <v>1300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>100</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
@@ -946,12 +953,12 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z9" s="3">
         <v>2500</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
@@ -970,59 +977,62 @@
       <c r="AF9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>114000</v>
+      </c>
+      <c r="E10" s="3">
         <v>3800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>210500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>73000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>11300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>53900</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1038,12 +1048,12 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z10" s="3">
         <v>24200</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1062,8 +1072,11 @@
       <c r="AF10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1096,100 +1109,104 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>111400</v>
+      </c>
+      <c r="E12" s="3">
         <v>130400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>120400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>114700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>141000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>130200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>125100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>107500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>92900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>90900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>92500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>108400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>107600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>122200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>104300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>102000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>122600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>90200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>92100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>86600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>68200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>57500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>55300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>95200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>42900</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>51200</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>31100</v>
       </c>
-      <c r="AD12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1280,50 +1297,53 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E14" s="3">
         <v>4700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-47400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-123400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>21900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-20500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>5600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>7700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>5000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>8400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>22700</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1345,26 +1365,26 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>400</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>2000</v>
       </c>
       <c r="AA14" s="3">
         <v>2000</v>
       </c>
       <c r="AB14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AC14" s="3">
         <v>-19300</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>3</v>
+      <c r="AD14" s="3">
+        <v>0</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>3</v>
@@ -1372,19 +1392,22 @@
       <c r="AF14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E15" s="3">
         <v>1400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1500</v>
-      </c>
-      <c r="F15" s="3">
-        <v>1600</v>
       </c>
       <c r="G15" s="3">
         <v>1600</v>
@@ -1402,7 +1425,7 @@
         <v>1600</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1464,8 +1487,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1495,192 +1521,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>220400</v>
+      </c>
+      <c r="E17" s="3">
         <v>227200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>189900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>174800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>207400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>178400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>161500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>144200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>124600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>131100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>129500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>153900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>175400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>178500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>151800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>148000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>168000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>127600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>128100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>124600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>102500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>92500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>81700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>133100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>63800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>46300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>41500</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-103800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-221300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-187100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-172600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-176700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-157400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-142600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-122800</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-129200</v>
       </c>
       <c r="M18" s="3">
         <v>-129200</v>
       </c>
       <c r="N18" s="3">
+        <v>-129200</v>
+      </c>
+      <c r="O18" s="3">
         <v>-80200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-173700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-165600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-149500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-94000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-167500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-127500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-120000</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X18" s="3">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-78700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-55000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-133100</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB18" s="3">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC18" s="3">
         <v>-46300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-41500</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1713,148 +1746,152 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E20" s="3">
         <v>15100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>8600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>8600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>8800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>97900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-7300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>28500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>6100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>3400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>700</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X20" s="3">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-7100</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB20" s="3">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>500</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-109800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-235000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-190400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-179600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>6700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-174600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-155700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-140900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-121500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-118900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-118700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>19300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-179100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-135600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-149700</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1873,15 +1910,15 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z21" s="3">
         <v>-58200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-139900</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1897,91 +1934,94 @@
       <c r="AF21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>42100</v>
+      </c>
+      <c r="E22" s="3">
         <v>29800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>23100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>22900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>23500</v>
-      </c>
-      <c r="H22" s="3">
-        <v>20300</v>
       </c>
       <c r="I22" s="3">
         <v>20300</v>
       </c>
       <c r="J22" s="3">
+        <v>20300</v>
+      </c>
+      <c r="K22" s="3">
         <v>20600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>20100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>20000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>19800</v>
-      </c>
-      <c r="N22" s="3">
-        <v>20300</v>
       </c>
       <c r="O22" s="3">
         <v>20300</v>
       </c>
       <c r="P22" s="3">
+        <v>20300</v>
+      </c>
+      <c r="Q22" s="3">
         <v>15100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>11100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>10800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>9700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>11000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>10900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>10800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>4000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>3000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>3600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1700</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>1200</v>
       </c>
       <c r="AC22" s="3">
         <v>1200</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>3</v>
+      <c r="AD22" s="3">
+        <v>1200</v>
       </c>
       <c r="AE22" s="3" t="s">
         <v>3</v>
@@ -1989,109 +2029,115 @@
       <c r="AF22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-169600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-266200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-164300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-75500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-36200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-170300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-179500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-160700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-142700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-140600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-140200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-201300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-152300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-161000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-102100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-171100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-135000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-130200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-136200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-104100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-84200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-60700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-143800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-69400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-49200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-42100</v>
       </c>
-      <c r="AD23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3">
         <v>1200</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2110,8 +2156,8 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -2173,8 +2219,11 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2265,192 +2314,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-169600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-267400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-164300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-75500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-36200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-170300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-179500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-160700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-142700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-140600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-140200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-201300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-152300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-161000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-102100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-171100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-135000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-130200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-136200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-104100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-84200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-60700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-143800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-69400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-49200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-42100</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-167400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-265100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-162000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-73500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-35200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-168100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-177000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-157900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-140200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-137600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-137300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-9900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-196400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-147200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-155900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-96300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-163100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-120000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-115900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-121000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-91900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-73500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-60000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-127100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-61200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-31400</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2541,8 +2599,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2633,8 +2694,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2725,8 +2789,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2817,192 +2884,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-15100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-8600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-8600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-8800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-97900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>7300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-28500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-6100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-3400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-700</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X32" s="3">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y32" s="3">
         <v>2500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>3600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>7100</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB32" s="3">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC32" s="3">
         <v>1800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-500</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-167400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-265100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-162000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-73500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-35200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-168100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-177000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-157900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-140200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-137600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-137300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-9900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-196400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-147200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-155900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-96300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-163100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-120000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-115900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-121000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-91900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-73500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-60000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-127100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-61200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-31400</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3093,197 +3169,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-167400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-265100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-162000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-73500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-35200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-168100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-177000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-157900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-140200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-137600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-137300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-9900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-196400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-147200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-155900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-96300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-163100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-120000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-115900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-121000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-91900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-73500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-60000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-127100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-61200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-31400</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AF38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3316,8 +3401,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3350,86 +3436,87 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>540600</v>
+      </c>
+      <c r="E41" s="3">
         <v>681100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>266300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>408000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>475200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>375900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>505200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>302400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>407400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>376700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>483200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>470100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>371600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>393800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>180300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>378400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>471200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>356100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>367000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>540900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>757000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>363800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>414000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>293800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>373000</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3442,8 +3529,11 @@
       <c r="AF41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3454,68 +3544,68 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>39800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>44500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>58900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>38100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>81400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>83900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>95200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>108700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>245600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>299700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>442900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>419300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>459200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>447900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>251000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>343700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>300000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>148100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>182200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>122100</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3534,38 +3624,41 @@
       <c r="AF42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>115300</v>
+      </c>
+      <c r="E43" s="3">
         <v>4700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>235500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>10800</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
       <c r="M43" s="3">
         <v>0</v>
       </c>
@@ -3575,27 +3668,27 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q43" s="3">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3">
         <v>500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>10200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>500</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U43" s="3">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V43" s="3">
         <v>8000</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3611,8 +3704,8 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB43" s="3">
-        <v>0</v>
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC43" s="3">
         <v>0</v>
@@ -3626,13 +3719,16 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>3</v>
+      <c r="D44" s="3">
+        <v>4000</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>3</v>
@@ -3655,8 +3751,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3718,20 +3814,23 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E45" s="3">
         <v>3700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>9500</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3747,57 +3846,57 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>76900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>50200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>55600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>45000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>52200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>39600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>62000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>25500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>35700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>26700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>21000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>19800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>22600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>22100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>12900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>9400</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3810,86 +3909,89 @@
       <c r="AF45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>695200</v>
+      </c>
+      <c r="E46" s="3">
         <v>720700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>444600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>616200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>783400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>477600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>587700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>432900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>552700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>548900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>642200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>771300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>716200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>888900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>639700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>909900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>945100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>642800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>745400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>861900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>925000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>568600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>558200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>306700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>382500</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3902,40 +4004,43 @@
       <c r="AF46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>128200</v>
+      </c>
+      <c r="E47" s="3">
         <v>143700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>160400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>117000</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3">
         <v>1600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>800</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3943,45 +4048,45 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q47" s="3">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3">
         <v>17700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>79600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>82200</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W47" s="3">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X47" s="3">
         <v>23200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>31100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>76800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>7500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>12500</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3994,85 +4099,88 @@
       <c r="AF47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E48" s="3">
         <v>12800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>15100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>17100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>19500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>19800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>21700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>22900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>24100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>25200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>27300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>29700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>31100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>46000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>44800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>42200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>35800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>36800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>25800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>26000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>24600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3000</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>1900</v>
       </c>
       <c r="AA48" s="3">
         <v>1900</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>3</v>
+      <c r="AB48" s="3">
+        <v>1900</v>
       </c>
       <c r="AC48" s="3" t="s">
         <v>3</v>
@@ -4086,56 +4194,59 @@
       <c r="AF48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>27800</v>
+      </c>
+      <c r="E49" s="3">
         <v>23900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>24500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>25100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>25700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>26300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>26900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>27500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>28100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>28700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>29300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>29900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>30500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>44900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>46200</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4151,8 +4262,8 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X49" s="3">
-        <v>0</v>
+      <c r="X49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y49" s="3">
         <v>0</v>
@@ -4178,8 +4289,11 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4270,8 +4384,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4362,86 +4479,89 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E52" s="3">
         <v>18200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>20300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>18900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>20700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>21000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>18200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>19600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>20800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>20200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>29900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>31300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>35300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>33000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>33100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>49800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>30200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>23900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>16500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>17300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>17000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>26300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>9500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>4600</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4454,8 +4574,11 @@
       <c r="AF52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4546,86 +4669,89 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>881600</v>
+      </c>
+      <c r="E54" s="3">
         <v>919300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>665000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>794400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>849300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>546400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>655000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>503700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>625700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>623000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>728700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>862200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>813100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1012800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>781500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1081500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1093300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>703600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>787700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>905200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>989800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>631700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>640500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>325500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>401400</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4638,8 +4764,11 @@
       <c r="AF54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4672,8 +4801,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4706,86 +4836,87 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>27500</v>
+      </c>
+      <c r="E57" s="3">
         <v>9600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>13400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>18100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>10700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>11900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>12000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>22300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>10300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>8900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>9800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>12800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>13100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>8900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>10300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>16100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>12300</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4798,49 +4929,52 @@
       <c r="AF57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E58" s="3">
         <v>4500</v>
-      </c>
-      <c r="E58" s="3">
-        <v>4600</v>
       </c>
       <c r="F58" s="3">
         <v>4600</v>
       </c>
       <c r="G58" s="3">
+        <v>4600</v>
+      </c>
+      <c r="H58" s="3">
         <v>4500</v>
-      </c>
-      <c r="H58" s="3">
-        <v>4100</v>
       </c>
       <c r="I58" s="3">
         <v>4100</v>
       </c>
       <c r="J58" s="3">
+        <v>4100</v>
+      </c>
+      <c r="K58" s="3">
         <v>3800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3700</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P58" s="3">
-        <v>300</v>
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q58" s="3">
         <v>300</v>
@@ -4849,14 +4983,14 @@
         <v>300</v>
       </c>
       <c r="S58" s="3">
+        <v>300</v>
+      </c>
+      <c r="T58" s="3">
         <v>3800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1600</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4872,8 +5006,8 @@
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB58" s="3">
         <v>0</v>
@@ -4890,86 +5024,89 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E59" s="3">
         <v>16200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>16600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>21500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>22700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>12100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>16800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>109900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>109000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>132400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>93400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>122900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>83500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>109300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>80500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>85100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>65900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>79800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>51800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>51500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>29600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>22600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>23100</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4982,86 +5119,89 @@
       <c r="AF59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>152100</v>
+      </c>
+      <c r="E60" s="3">
         <v>154400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>139200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>134400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>141500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>143800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>106100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>110100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>96600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>121400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>119200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>141200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>103500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>135100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>95800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>131900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>94700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>95600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>75700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>92600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>64900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>60400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>39900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>38700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>35500</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5074,86 +5214,89 @@
       <c r="AF60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1853000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1726100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1725100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1724700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1724200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1735700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1730900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1729900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1725200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1707600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1698700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1693200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1708100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1705100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1376600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1375300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1362700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>477400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>471900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>466600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>461300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>91800</v>
-      </c>
-      <c r="Y61" s="3">
-        <v>75000</v>
       </c>
       <c r="Z61" s="3">
         <v>75000</v>
       </c>
       <c r="AA61" s="3">
+        <v>75000</v>
+      </c>
+      <c r="AB61" s="3">
         <v>54900</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
         <v>0</v>
       </c>
@@ -5166,86 +5309,89 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>497700</v>
+      </c>
+      <c r="E62" s="3">
         <v>479400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>7600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>10600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>38900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>41200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>42900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>42300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>38300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>44900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>29900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>24000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>22600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>21700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>18500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>11500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>400</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5258,8 +5404,11 @@
       <c r="AF62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5350,8 +5499,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5442,8 +5594,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5534,86 +5689,89 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2520300</v>
+      </c>
+      <c r="E66" s="3">
         <v>2377000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1883400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1876500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1886200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1888900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1848700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1853300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1839300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1877700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1867200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1887800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1854100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1883200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1524900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1545800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1488600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>645700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>623900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>639500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>609100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>223200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>180800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>162600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>149200</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5626,8 +5784,11 @@
       <c r="AF66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5660,8 +5821,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5752,8 +5914,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5844,8 +6009,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5916,13 +6084,13 @@
         <v>0</v>
       </c>
       <c r="Z70" s="3">
-        <v>479000</v>
+        <v>0</v>
       </c>
       <c r="AA70" s="3">
         <v>479000</v>
       </c>
       <c r="AB70" s="3">
-        <v>0</v>
+        <v>479000</v>
       </c>
       <c r="AC70" s="3">
         <v>0</v>
@@ -5936,8 +6104,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6028,86 +6199,89 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-3263700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-3096300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2831200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2669200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2595700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2560500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2392400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2215400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2057500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1918100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1780600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1643200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1633400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1437000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1289800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1133900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1037500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-888800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-768800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-652900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-531900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-440000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-366600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-319500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-230300</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6120,8 +6294,11 @@
       <c r="AF72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6212,8 +6389,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6304,8 +6484,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6396,86 +6579,89 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1648400</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1467900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1229900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-1092900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-1049500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-1354300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-1207500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-1362000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-1225700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-1254600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-1138400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-1025500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-1041000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-870400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-743400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-464300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-395300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>57900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>163800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>265800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>380700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>408500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>459800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-316100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-226900</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6488,8 +6674,11 @@
       <c r="AF76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6580,197 +6769,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AF80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-167400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-265100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-162000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-73500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-35200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-168100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-177000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-157900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-140200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-137600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-137300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-9900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-196400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-147200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-155900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-96300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-163100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-120000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-115900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-121000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-91900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-73500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-60000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-127100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-61200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-31400</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6803,8 +7001,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6821,38 +7020,38 @@
         <v>1000</v>
       </c>
       <c r="H83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I83" s="3">
         <v>1100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1700</v>
-      </c>
-      <c r="M83" s="3">
-        <v>1600</v>
       </c>
       <c r="N83" s="3">
         <v>1600</v>
       </c>
       <c r="O83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="P83" s="3">
         <v>1900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>300</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6871,18 +7070,18 @@
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z83" s="3">
         <v>400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>100</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6895,8 +7094,11 @@
       <c r="AF83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6987,8 +7189,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7079,8 +7284,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7171,8 +7379,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7263,8 +7474,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7355,86 +7569,89 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-199200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-195300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-180600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>74700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-219500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-124800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-145200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-113400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-144300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-93200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-135200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-30500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-160600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-133900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-121600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-91700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-150800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-96300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-131700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-87800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-83900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-76200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-50000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-127400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-59100</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7447,8 +7664,11 @@
       <c r="AF89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7481,25 +7701,26 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F91" s="3">
         <v>-100</v>
       </c>
       <c r="G91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H91" s="3">
         <v>-700</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-400</v>
       </c>
       <c r="I91" s="3">
         <v>-400</v>
@@ -7508,59 +7729,59 @@
         <v>-400</v>
       </c>
       <c r="K91" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="L91" s="3">
-        <v>-800</v>
+        <v>0</v>
       </c>
       <c r="M91" s="3">
         <v>-800</v>
       </c>
       <c r="N91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="O91" s="3">
         <v>-3900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-6500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-4500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-400</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
@@ -7573,8 +7794,11 @@
       <c r="AF91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7665,8 +7889,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7757,86 +7984,89 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>38200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>3000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>22800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>37700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>4100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>12300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>18000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>146900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>149700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>138600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>21800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>59000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-282100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>83000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-45100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-129000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>38000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-16900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-197300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7849,8 +8079,11 @@
       <c r="AF94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7883,8 +8116,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7912,8 +8146,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7975,8 +8209,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8067,8 +8304,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8159,8 +8399,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8251,86 +8494,89 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>60300</v>
+      </c>
+      <c r="E100" s="3">
         <v>473900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-5700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>279500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>307000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>150200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>6400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-20800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>325400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-135500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>547900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>4500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>439200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>42900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>367500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-11600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
@@ -8343,8 +8589,11 @@
       <c r="AF100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8372,8 +8621,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -8435,86 +8684,89 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-140500</v>
+      </c>
+      <c r="E102" s="3">
         <v>275400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-141600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>72000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>82800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-129400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>199500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-110500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>18200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-68900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>13100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>98500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-22200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>213300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-198000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-92600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>115100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-8700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-174000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-216100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>393300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-50200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>120200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-142000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-63200</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
@@ -8525,6 +8777,9 @@
         <v>3</v>
       </c>
       <c r="AF102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BBIO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BBIO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="92">
   <si>
     <t>BBIO</t>
   </si>
@@ -656,228 +656,232 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AG7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>110600</v>
+      </c>
+      <c r="E8" s="3">
         <v>116600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>211100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>73700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>12900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>54000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8100</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z8" s="3">
         <v>13800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>26700</v>
       </c>
-      <c r="AA8" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC8" s="3">
-        <v>0</v>
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD8" s="3">
         <v>0</v>
       </c>
-      <c r="AE8" s="3" t="s">
-        <v>3</v>
+      <c r="AE8" s="3">
+        <v>0</v>
       </c>
       <c r="AF8" s="3" t="s">
         <v>3</v>
@@ -885,19 +889,22 @@
       <c r="AG8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E9" s="3">
         <v>2600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2100</v>
-      </c>
-      <c r="F9" s="3">
-        <v>600</v>
       </c>
       <c r="G9" s="3">
         <v>600</v>
@@ -915,32 +922,32 @@
         <v>600</v>
       </c>
       <c r="L9" s="3">
+        <v>600</v>
+      </c>
+      <c r="M9" s="3">
         <v>700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>600</v>
-      </c>
-      <c r="N9" s="3">
-        <v>700</v>
       </c>
       <c r="O9" s="3">
         <v>700</v>
       </c>
       <c r="P9" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q9" s="3">
         <v>1300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>100</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
@@ -956,12 +963,12 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA9" s="3">
         <v>2500</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
@@ -980,62 +987,65 @@
       <c r="AG9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>106900</v>
+      </c>
+      <c r="E10" s="3">
         <v>114000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>210500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>73000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>11300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>53900</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1051,12 +1061,12 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA10" s="3">
         <v>24200</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1075,8 +1085,11 @@
       <c r="AG10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1110,103 +1123,107 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>111200</v>
+      </c>
+      <c r="E12" s="3">
         <v>111400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>130400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>120400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>114700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>141000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>130200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>125100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>107500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>92900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>90900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>92500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>108400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>107600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>122200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>104300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>102000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>122600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>90200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>92100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>86600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>68200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>57500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>55300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>95200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>42900</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>51200</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>31100</v>
       </c>
-      <c r="AE12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1300,53 +1317,56 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>800</v>
+      </c>
+      <c r="E14" s="3">
         <v>21700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>4700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-47400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-123400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>21900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-20500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>5600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>7700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>5000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>8400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>22700</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1368,26 +1388,26 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>400</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>2000</v>
       </c>
       <c r="AB14" s="3">
         <v>2000</v>
       </c>
       <c r="AC14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AD14" s="3">
         <v>-19300</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="3" t="s">
-        <v>3</v>
+      <c r="AE14" s="3">
+        <v>0</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>3</v>
@@ -1395,8 +1415,11 @@
       <c r="AG14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1404,13 +1427,13 @@
         <v>1300</v>
       </c>
       <c r="E15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F15" s="3">
         <v>1400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1500</v>
-      </c>
-      <c r="G15" s="3">
-        <v>1600</v>
       </c>
       <c r="H15" s="3">
         <v>1600</v>
@@ -1428,7 +1451,7 @@
         <v>1600</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1490,8 +1513,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1522,198 +1548,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>244000</v>
+      </c>
+      <c r="E17" s="3">
         <v>220400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>227200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>189900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>174800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>207400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>178400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>161500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>144200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>124600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>131100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>129500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>153900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>175400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>178500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>151800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>148000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>168000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>127600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>128100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>124600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>102500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>92500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>81700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>133100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>63800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>46300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>41500</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-133500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-103800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-221300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-187100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-172600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-176700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-157400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-142600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-122800</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-129200</v>
       </c>
       <c r="N18" s="3">
         <v>-129200</v>
       </c>
       <c r="O18" s="3">
+        <v>-129200</v>
+      </c>
+      <c r="P18" s="3">
         <v>-80200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-173700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-165600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-149500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-94000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-167500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-127500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-120000</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z18" s="3">
         <v>-78700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-55000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-133100</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC18" s="3">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD18" s="3">
         <v>-46300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-41500</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1747,154 +1780,158 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E20" s="3">
         <v>7300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>15100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>4800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>8600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>8600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>8800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>97900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>28500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>6100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>3400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>700</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-7100</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC20" s="3">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>500</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-145800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-109800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-235000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-190400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-179600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>6700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-174600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-155700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-140900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-121500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-118900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-118700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>19300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-179100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-135600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-149700</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1913,15 +1950,15 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA21" s="3">
         <v>-58200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-139900</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1937,94 +1974,97 @@
       <c r="AG21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>37600</v>
+      </c>
+      <c r="E22" s="3">
         <v>42100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>29800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>23100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>22900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>23500</v>
-      </c>
-      <c r="I22" s="3">
-        <v>20300</v>
       </c>
       <c r="J22" s="3">
         <v>20300</v>
       </c>
       <c r="K22" s="3">
+        <v>20300</v>
+      </c>
+      <c r="L22" s="3">
         <v>20600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>20100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>20000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>19800</v>
-      </c>
-      <c r="O22" s="3">
-        <v>20300</v>
       </c>
       <c r="P22" s="3">
         <v>20300</v>
       </c>
       <c r="Q22" s="3">
+        <v>20300</v>
+      </c>
+      <c r="R22" s="3">
         <v>15100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>11100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>10800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>9700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>11000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>10900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>10800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>4000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>3000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>2100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>3600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1700</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>1200</v>
       </c>
       <c r="AD22" s="3">
         <v>1200</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>3</v>
+      <c r="AE22" s="3">
+        <v>1200</v>
       </c>
       <c r="AF22" s="3" t="s">
         <v>3</v>
@@ -2032,115 +2072,121 @@
       <c r="AG22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-181700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-169600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-266200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-164300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-75500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-36200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-170300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-179500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-160700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-142700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-140600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-140200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-201300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-152300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-161000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-102100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-171100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-135000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-130200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-136200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-104100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-84200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-60700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-143800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-69400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-49200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-42100</v>
       </c>
-      <c r="AE23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="3">
+      <c r="D24" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3">
         <v>1200</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2159,8 +2205,8 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -2222,8 +2268,11 @@
       <c r="AG24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2317,198 +2366,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-183800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-169600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-267400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-164300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-75500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-36200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-170300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-179500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-160700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-142700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-140600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-140200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-201300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-152300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-161000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-102100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-171100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-135000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-130200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-136200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-104100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-84200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-60700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-143800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-69400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-49200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-42100</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-181900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-167400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-265100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-162000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-73500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-35200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-168100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-177000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-157900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-140200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-137600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-137300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-9900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-196400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-147200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-155900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-96300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-163100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-120000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-115900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-121000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-91900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-73500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-60000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-127100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-61200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-31400</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2602,8 +2660,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2697,8 +2758,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2792,8 +2856,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2887,198 +2954,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-7300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-15100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-4800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-8600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-8600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-8800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-97900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>7300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-28500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-6100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-3400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-700</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z32" s="3">
         <v>2500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>3600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>7100</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC32" s="3">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD32" s="3">
         <v>1800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-500</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-181900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-167400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-265100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-162000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-73500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-35200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-168100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-177000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-157900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-140200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-137600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-137300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-9900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-196400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-147200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-155900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-96300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-163100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-120000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-115900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-121000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-91900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-73500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-60000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-127100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-61200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-31400</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3172,203 +3248,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-181900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-167400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-265100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-162000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-73500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-35200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-168100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-177000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-157900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-140200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-137600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-137300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-9900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-196400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-147200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-155900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-96300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-163100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-120000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-115900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-121000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-91900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-73500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-60000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-127100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-61200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-31400</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AG38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3402,8 +3487,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3437,89 +3523,90 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>749000</v>
+      </c>
+      <c r="E41" s="3">
         <v>540600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>681100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>266300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>408000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>475200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>375900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>505200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>302400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>407400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>376700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>483200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>470100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>371600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>393800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>180300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>378400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>471200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>356100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>367000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>540900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>757000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>363800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>414000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>293800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>373000</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3532,13 +3619,16 @@
       <c r="AG41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>7900</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -3547,68 +3637,68 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>39800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>44500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>58900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>38100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>81400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>83900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>95200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>108700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>245600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>299700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>442900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>419300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>459200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>447900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>251000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>343700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>300000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>148100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>182200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>122100</v>
       </c>
-      <c r="AA42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3627,41 +3717,44 @@
       <c r="AG42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>76900</v>
+      </c>
+      <c r="E43" s="3">
         <v>115300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>235500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>10800</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
       <c r="N43" s="3">
         <v>0</v>
       </c>
@@ -3671,27 +3764,27 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R43" s="3">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S43" s="3">
         <v>500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>10200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>500</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V43" s="3">
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W43" s="3">
         <v>8000</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3707,8 +3800,8 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC43" s="3">
-        <v>0</v>
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD43" s="3">
         <v>0</v>
@@ -3722,17 +3815,20 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E44" s="3">
         <v>4000</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3754,8 +3850,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3817,23 +3913,26 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E45" s="3">
         <v>3100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>9500</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3849,57 +3948,57 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>76900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>50200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>55600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>45000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>52200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>39600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>62000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>25500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>35700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>26700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>21000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>19800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>22600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>22100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>12900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>9400</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3912,89 +4011,92 @@
       <c r="AG45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>912300</v>
+      </c>
+      <c r="E46" s="3">
         <v>695200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>720700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>444600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>616200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>783400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>477600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>587700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>432900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>552700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>548900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>642200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>771300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>716200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>888900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>639700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>909900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>945100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>642800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>745400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>861900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>925000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>568600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>558200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>306700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>382500</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4007,43 +4109,46 @@
       <c r="AG46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>108000</v>
+      </c>
+      <c r="E47" s="3">
         <v>128200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>143700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>160400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>117000</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3">
         <v>1600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>800</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -4051,45 +4156,45 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R47" s="3">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S47" s="3">
         <v>17700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>79600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>82200</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X47" s="3">
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y47" s="3">
         <v>23200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>31100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>76800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>7500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>12500</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4102,88 +4207,91 @@
       <c r="AG47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E48" s="3">
         <v>13900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>12800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>15100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>17100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>19500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>19800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>21700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>22900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>24100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>25200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>27300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>29700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>31100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>46000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>44800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>42200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>35800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>36800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>25800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>26000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>24600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3000</v>
-      </c>
-      <c r="AA48" s="3">
-        <v>1900</v>
       </c>
       <c r="AB48" s="3">
         <v>1900</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>3</v>
+      <c r="AC48" s="3">
+        <v>1900</v>
       </c>
       <c r="AD48" s="3" t="s">
         <v>3</v>
@@ -4197,59 +4305,62 @@
       <c r="AG48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>29500</v>
+      </c>
+      <c r="E49" s="3">
         <v>27800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>23900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>24500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>25100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>25700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>26300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>26900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>27500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>28100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>28700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>29300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>29900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>30500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>44900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>46200</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4265,8 +4376,8 @@
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y49" s="3">
-        <v>0</v>
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z49" s="3">
         <v>0</v>
@@ -4292,8 +4403,11 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4387,8 +4501,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4482,89 +4599,92 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E52" s="3">
         <v>16600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>18200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>20300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>18900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>20700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>21000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>18200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>19600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>20800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>20200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>29900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>31300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>35300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>33000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>33100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>49800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>30200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>23900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>16500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>17300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>17000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>26300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>9500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>4600</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4577,8 +4697,11 @@
       <c r="AG52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4672,89 +4795,92 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1080200</v>
+      </c>
+      <c r="E54" s="3">
         <v>881600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>919300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>665000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>794400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>849300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>546400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>655000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>503700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>625700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>623000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>728700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>862200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>813100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1012800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>781500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1081500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1093300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>703600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>787700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>905200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>989800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>631700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>640500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>325500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>401400</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4767,8 +4893,11 @@
       <c r="AG54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4802,8 +4931,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4837,89 +4967,90 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E57" s="3">
         <v>27500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>9600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>13400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>18100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>10700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>11600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>10100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>11900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>12000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>22300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>10300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>8900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>9800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>12800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>13100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>8900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>10300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>16100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>12300</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4932,52 +5063,55 @@
       <c r="AG57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E58" s="3">
         <v>5200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4500</v>
-      </c>
-      <c r="F58" s="3">
-        <v>4600</v>
       </c>
       <c r="G58" s="3">
         <v>4600</v>
       </c>
       <c r="H58" s="3">
+        <v>4600</v>
+      </c>
+      <c r="I58" s="3">
         <v>4500</v>
-      </c>
-      <c r="I58" s="3">
-        <v>4100</v>
       </c>
       <c r="J58" s="3">
         <v>4100</v>
       </c>
       <c r="K58" s="3">
+        <v>4100</v>
+      </c>
+      <c r="L58" s="3">
         <v>3800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3700</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>300</v>
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R58" s="3">
         <v>300</v>
@@ -4986,14 +5120,14 @@
         <v>300</v>
       </c>
       <c r="T58" s="3">
+        <v>300</v>
+      </c>
+      <c r="U58" s="3">
         <v>3800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1600</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5009,8 +5143,8 @@
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB58" s="3">
-        <v>0</v>
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC58" s="3">
         <v>0</v>
@@ -5027,89 +5161,92 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E59" s="3">
         <v>16100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>16200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>16600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>21500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>22700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>12600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>16800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>109900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>109000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>132400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>93400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>122900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>83500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>109300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>80500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>85100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>65900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>79800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>51800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>51500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>29600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>22600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>23100</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5122,89 +5259,92 @@
       <c r="AG59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>175900</v>
+      </c>
+      <c r="E60" s="3">
         <v>152100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>154400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>139200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>134400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>141500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>143800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>106100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>110100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>96600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>121400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>119200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>141200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>103500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>135100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>95800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>131900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>94700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>95600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>75700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>92600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>64900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>60400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>39900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>38700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>35500</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5217,89 +5357,92 @@
       <c r="AG60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1853600</v>
+      </c>
+      <c r="E61" s="3">
         <v>1853000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1726100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1725100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1724700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1724200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1735700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1730900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1729900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1725200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1707600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1698700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1693200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1708100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1705100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1376600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1375300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1362700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>477400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>471900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>466600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>461300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>91800</v>
-      </c>
-      <c r="Z61" s="3">
-        <v>75000</v>
       </c>
       <c r="AA61" s="3">
         <v>75000</v>
       </c>
       <c r="AB61" s="3">
+        <v>75000</v>
+      </c>
+      <c r="AC61" s="3">
         <v>54900</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
@@ -5312,89 +5455,92 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>814500</v>
+      </c>
+      <c r="E62" s="3">
         <v>497700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>479400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>10600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>38900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>41200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>42900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>42300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>38300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>44900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>29900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>24000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>22600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>21700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>18500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>11500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>400</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5407,8 +5553,11 @@
       <c r="AG62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5502,8 +5651,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5597,8 +5749,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5692,89 +5847,92 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2858600</v>
+      </c>
+      <c r="E66" s="3">
         <v>2520300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2377000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1883400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1876500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1886200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1888900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1848700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1853300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1839300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1877700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1867200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1887800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1854100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1883200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1524900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1545800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1488600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>645700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>623900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>639500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>609100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>223200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>180800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>162600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>149200</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5787,8 +5945,11 @@
       <c r="AG66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5822,8 +5983,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5917,8 +6079,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6012,8 +6177,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6087,13 +6255,13 @@
         <v>0</v>
       </c>
       <c r="AA70" s="3">
-        <v>479000</v>
+        <v>0</v>
       </c>
       <c r="AB70" s="3">
         <v>479000</v>
       </c>
       <c r="AC70" s="3">
-        <v>0</v>
+        <v>479000</v>
       </c>
       <c r="AD70" s="3">
         <v>0</v>
@@ -6107,8 +6275,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6202,89 +6373,92 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-3445600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-3263700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-3096300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2831200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2669200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2595700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2560500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2392400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2215400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2057500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1918100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1780600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1643200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1633400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1437000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1289800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1133900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1037500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-888800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-768800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-652900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-531900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-440000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-366600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-319500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-230300</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6297,8 +6471,11 @@
       <c r="AG72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6392,8 +6569,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6487,8 +6667,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6582,89 +6765,92 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1787900</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1648400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1467900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-1229900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-1092900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-1049500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-1354300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-1207500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-1362000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-1225700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-1254600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-1138400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-1025500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-1041000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-870400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-743400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-464300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-395300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>57900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>163800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>265800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>380700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>408500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>459800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-316100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-226900</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6677,8 +6863,11 @@
       <c r="AG76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6772,203 +6961,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AG80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-181900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-167400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-265100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-162000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-73500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-35200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-168100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-177000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-157900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-140200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-137600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-137300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-9900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-196400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-147200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-155900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-96300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-163100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-120000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-115900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-121000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-91900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-73500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-60000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-127100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-61200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-31400</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7002,8 +7200,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7023,38 +7222,38 @@
         <v>1000</v>
       </c>
       <c r="I83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J83" s="3">
         <v>1100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1700</v>
-      </c>
-      <c r="N83" s="3">
-        <v>1600</v>
       </c>
       <c r="O83" s="3">
         <v>1600</v>
       </c>
       <c r="P83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="Q83" s="3">
         <v>1900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>300</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
@@ -7073,18 +7272,18 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA83" s="3">
         <v>400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>100</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
@@ -7097,8 +7296,11 @@
       <c r="AG83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7192,8 +7394,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7287,8 +7492,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7382,8 +7590,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7477,8 +7688,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7572,89 +7786,92 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-80700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-199200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-195300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-180600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>74700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-219500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-124800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-145200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-113400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-144300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-93200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-135200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-30500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-160600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-133900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-121600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-91700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-150800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-96300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-131700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-87800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-83900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-76200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-50000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-127400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-59100</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7667,8 +7884,11 @@
       <c r="AG89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7702,28 +7922,29 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
+      <c r="D91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G91" s="3">
         <v>-100</v>
       </c>
       <c r="H91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I91" s="3">
         <v>-700</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-400</v>
       </c>
       <c r="J91" s="3">
         <v>-400</v>
@@ -7732,59 +7953,59 @@
         <v>-400</v>
       </c>
       <c r="L91" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="M91" s="3">
-        <v>-800</v>
+        <v>0</v>
       </c>
       <c r="N91" s="3">
         <v>-800</v>
       </c>
       <c r="O91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="P91" s="3">
         <v>-3900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-6500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-400</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD91" s="3" t="s">
         <v>3</v>
       </c>
@@ -7797,8 +8018,11 @@
       <c r="AG91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7892,8 +8116,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7987,89 +8214,92 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>38200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>3000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>22800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>37700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>4100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>12300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>18000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>146900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>149700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>138600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>21800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>59000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-282100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>83000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-45100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-129000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>38000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-16900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-197300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
@@ -8082,8 +8312,11 @@
       <c r="AG94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8117,8 +8350,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8149,8 +8383,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -8212,8 +8446,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8307,8 +8544,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8402,8 +8642,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8497,89 +8740,92 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>302000</v>
+      </c>
+      <c r="E100" s="3">
         <v>60300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>473900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-5700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>279500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>307000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>150200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>6400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-20800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>325400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-135500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>547900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>4500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>439200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>42900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>367500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-11600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
@@ -8592,8 +8838,11 @@
       <c r="AG100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8624,8 +8873,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -8687,89 +8936,92 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>208400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-140500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>275400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-141600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>72000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>82800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-129400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>199500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-110500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>18200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-68900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>13100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>98500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-22200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>213300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-198000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-92600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>115100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-8700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-174000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-216100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>393300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-50200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>120200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-142000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-63200</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
@@ -8780,6 +9032,9 @@
         <v>3</v>
       </c>
       <c r="AG102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BBIO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BBIO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="92">
   <si>
     <t>BBIO</t>
   </si>
@@ -656,242 +656,245 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="35" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="36" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AI7" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AJ7" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>154200</v>
+      </c>
+      <c r="E8" s="3">
         <v>120700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>110600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>116600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>211100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>73700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>12900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>54000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>8100</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB8" s="3">
         <v>13800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>26700</v>
       </c>
-      <c r="AC8" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE8" s="3">
-        <v>0</v>
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF8" s="3">
         <v>0</v>
       </c>
-      <c r="AG8" s="3" t="s">
-        <v>3</v>
+      <c r="AG8" s="3">
+        <v>0</v>
       </c>
       <c r="AH8" s="3" t="s">
         <v>3</v>
@@ -899,25 +902,28 @@
       <c r="AI8" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ8" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E9" s="3">
         <v>6600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2100</v>
-      </c>
-      <c r="H9" s="3">
-        <v>600</v>
       </c>
       <c r="I9" s="3">
         <v>600</v>
@@ -935,32 +941,32 @@
         <v>600</v>
       </c>
       <c r="N9" s="3">
+        <v>600</v>
+      </c>
+      <c r="O9" s="3">
         <v>700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>600</v>
-      </c>
-      <c r="P9" s="3">
-        <v>700</v>
       </c>
       <c r="Q9" s="3">
         <v>700</v>
       </c>
       <c r="R9" s="3">
+        <v>700</v>
+      </c>
+      <c r="S9" s="3">
         <v>1300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>100</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
@@ -976,12 +982,12 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC9" s="3">
         <v>2500</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
@@ -1000,68 +1006,71 @@
       <c r="AI9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>146100</v>
+      </c>
+      <c r="E10" s="3">
         <v>114100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>106900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>114000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>210500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>73000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>11300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>53900</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1077,12 +1086,12 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC10" s="3">
         <v>24200</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1101,8 +1110,11 @@
       <c r="AI10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1138,109 +1150,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>116400</v>
+      </c>
+      <c r="E12" s="3">
         <v>112900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>111200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>111400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>130400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>120400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>114700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>141000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>130200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>125100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>107500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>92900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>90900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>92500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>108400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>107600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>122200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>104300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>102000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>122600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>90200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>92100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>86600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>68200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>57500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>55300</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>95200</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>42900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>51200</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>31100</v>
       </c>
-      <c r="AG12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1340,59 +1356,62 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E14" s="3">
         <v>8800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>21700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-47400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-123400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>21900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-20500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>5600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>3600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>7700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>5000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>8400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>22700</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1414,26 +1433,26 @@
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>400</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>2000</v>
       </c>
       <c r="AD14" s="3">
         <v>2000</v>
       </c>
       <c r="AE14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AF14" s="3">
         <v>-19300</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="3" t="s">
-        <v>3</v>
+      <c r="AG14" s="3">
+        <v>0</v>
       </c>
       <c r="AH14" s="3" t="s">
         <v>3</v>
@@ -1441,8 +1460,11 @@
       <c r="AI14" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ14" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1450,19 +1472,19 @@
         <v>1400</v>
       </c>
       <c r="E15" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="F15" s="3">
         <v>1300</v>
       </c>
       <c r="G15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H15" s="3">
         <v>1400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1500</v>
-      </c>
-      <c r="I15" s="3">
-        <v>1600</v>
       </c>
       <c r="J15" s="3">
         <v>1600</v>
@@ -1480,7 +1502,7 @@
         <v>1600</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1542,8 +1564,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1576,210 +1601,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>282600</v>
+      </c>
+      <c r="E17" s="3">
         <v>257100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>244000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>220400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>227200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>189900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>174800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>207400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>178400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>161500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>144200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>124600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>131100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>129500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>153900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>175400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>178500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>151800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>148000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>168000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>127600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>128100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>124600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>102500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>92500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>81700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>133100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>63800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>46300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>41500</v>
       </c>
-      <c r="AG17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI17" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ17" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-128400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-136400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-133500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-103800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-221300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-187100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-172600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-176700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-157400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-142600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-122800</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-129200</v>
       </c>
       <c r="P18" s="3">
         <v>-129200</v>
       </c>
       <c r="Q18" s="3">
+        <v>-129200</v>
+      </c>
+      <c r="R18" s="3">
         <v>-80200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-173700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-165600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-149500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-94000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-167500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-127500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-120000</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB18" s="3">
         <v>-78700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-55000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-133100</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE18" s="3">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF18" s="3">
         <v>-46300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-41500</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI18" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ18" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1815,166 +1847,170 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>13600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>7300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>15100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>4800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>8600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>8600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>8800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>97900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-7300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>28500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>6100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>3400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>700</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-7100</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE20" s="3">
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-1800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>500</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI20" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ20" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-136200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-134300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-145800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-109800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-235000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-190400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-179600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>6700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-174600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-155700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-140900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-121500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-118900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-118700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>19300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-179100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-135600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-149700</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1993,15 +2029,15 @@
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC21" s="3">
         <v>-58200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-139900</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
@@ -2017,100 +2053,103 @@
       <c r="AI21" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ21" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>50300</v>
+      </c>
+      <c r="E22" s="3">
         <v>48100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>37600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>42100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>29800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>23100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>22900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>23500</v>
-      </c>
-      <c r="K22" s="3">
-        <v>20300</v>
       </c>
       <c r="L22" s="3">
         <v>20300</v>
       </c>
       <c r="M22" s="3">
+        <v>20300</v>
+      </c>
+      <c r="N22" s="3">
         <v>20600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>20100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>20000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>19800</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>20300</v>
       </c>
       <c r="R22" s="3">
         <v>20300</v>
       </c>
       <c r="S22" s="3">
+        <v>20300</v>
+      </c>
+      <c r="T22" s="3">
         <v>15100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>11100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>10800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>9700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>11000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>10900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>10800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>4000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>3000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>2100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>3600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>1700</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>1200</v>
       </c>
       <c r="AF22" s="3">
         <v>1200</v>
       </c>
-      <c r="AG22" s="3" t="s">
-        <v>3</v>
+      <c r="AG22" s="3">
+        <v>1200</v>
       </c>
       <c r="AH22" s="3" t="s">
         <v>3</v>
@@ -2118,127 +2157,133 @@
       <c r="AI22" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ22" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-194800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-186500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-181700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-169600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-266200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-164300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-75500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-36200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-170300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-179500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-160700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-142700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-140600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-140200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-201300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-152300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-161000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-102100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-171100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-135000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-130200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-136200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-104100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-84200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-60700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-143800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-69400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-49200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-42100</v>
       </c>
-      <c r="AG23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI23" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ23" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2100</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3">
         <v>1200</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2257,8 +2302,8 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -2320,8 +2365,11 @@
       <c r="AI24" s="3">
         <v>0</v>
       </c>
+      <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2421,210 +2469,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-194600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-184900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-183800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-169600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-267400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-164300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-75500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-36200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-170300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-179500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-160700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-142700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-140600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-140200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-201300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-152300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-161000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-102100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-171100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-135000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-130200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-136200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-104100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-84200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-60700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-143800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-69400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-49200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-42100</v>
       </c>
-      <c r="AG26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI26" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ26" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-192900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-182700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-181900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-167400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-265100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-162000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-73500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-35200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-168100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-177000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-157900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-140200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-137600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-137300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-9900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-196400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-147200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-155900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-96300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-163100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-120000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-115900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-121000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-91900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-73500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-60000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-127100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-61200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-31400</v>
       </c>
-      <c r="AG27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI27" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ27" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2724,8 +2781,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2825,8 +2885,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2926,8 +2989,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3027,210 +3093,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E32" s="3">
         <v>600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-13600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-7300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-15100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-4800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-8600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-8600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-8800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-97900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>7300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-28500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-6100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-3400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-700</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB32" s="3">
         <v>2500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>3600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>7100</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE32" s="3">
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF32" s="3">
         <v>1800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-500</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI32" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ32" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-192900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-182700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-181900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-167400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-265100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-162000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-73500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-35200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-168100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-177000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-157900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-140200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-137600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-137300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-9900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-196400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-147200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-155900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-96300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-163100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-120000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-115900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-121000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-91900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-73500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-60000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-127100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-61200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-31400</v>
       </c>
-      <c r="AG33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI33" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ33" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3330,215 +3405,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-192900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-182700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-181900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-167400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-265100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-162000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-73500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-35200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-168100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-177000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-157900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-140200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-137600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-137300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-9900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-196400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-147200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-155900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-96300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-163100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-120000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-115900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-121000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-91900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-73500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-60000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-127100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-61200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-31400</v>
       </c>
-      <c r="AG35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI35" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ35" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AI38" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AJ38" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3574,8 +3658,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3611,95 +3696,96 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>570100</v>
+      </c>
+      <c r="E41" s="3">
         <v>643000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>749000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>540600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>681100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>266300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>408000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>475200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>375900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>505200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>302400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>407400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>376700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>483200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>470100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>371600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>393800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>180300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>378400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>471200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>356100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>367000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>540900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>757000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>363800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>414000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>293800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>373000</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3712,20 +3798,23 @@
       <c r="AI41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E42" s="3">
         <v>3000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>7900</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
@@ -3733,68 +3822,68 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>39800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>44500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>58900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>38100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>81400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>83900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>95200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>108700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>245600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>299700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>442900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>419300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>459200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>447900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>251000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>343700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>300000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>148100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>182200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>122100</v>
       </c>
-      <c r="AC42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3813,47 +3902,50 @@
       <c r="AI42" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ42" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>139400</v>
+      </c>
+      <c r="E43" s="3">
         <v>116500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>76900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>115300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>235500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>8600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>10800</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
       <c r="P43" s="3">
         <v>0</v>
       </c>
@@ -3863,27 +3955,27 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T43" s="3">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U43" s="3">
         <v>500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>10200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>500</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X43" s="3">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y43" s="3">
         <v>8000</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3899,8 +3991,8 @@
       <c r="AD43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE43" s="3">
-        <v>0</v>
+      <c r="AE43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF43" s="3">
         <v>0</v>
@@ -3914,23 +4006,26 @@
       <c r="AI43" s="3">
         <v>0</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>26800</v>
+      </c>
+      <c r="E44" s="3">
         <v>24500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>18300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4000</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3952,8 +4047,8 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -4015,29 +4110,32 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>4900</v>
+        <v>5100</v>
       </c>
       <c r="E45" s="3">
         <v>4900</v>
       </c>
       <c r="F45" s="3">
+        <v>4900</v>
+      </c>
+      <c r="G45" s="3">
         <v>3100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>9500</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4053,57 +4151,57 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
         <v>76900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>50200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>55600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>45000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>52200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>39600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>62000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>25500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>35700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>26700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>21000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>19800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>22600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>22100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>12900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>9400</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4116,95 +4214,98 @@
       <c r="AI45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>797700</v>
+      </c>
+      <c r="E46" s="3">
         <v>839400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>912300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>695200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>720700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>444600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>616200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>783400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>477600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>587700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>432900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>552700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>548900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>642200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>771300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>716200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>888900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>639700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>909900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>945100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>642800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>745400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>861900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>925000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>568600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>558200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>306700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>382500</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4217,49 +4318,52 @@
       <c r="AI46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>80000</v>
+      </c>
+      <c r="E47" s="3">
         <v>92200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>108000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>128200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>143700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>160400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>117000</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3">
         <v>1600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>800</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4267,45 +4371,45 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T47" s="3">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U47" s="3">
         <v>17700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>79600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>82200</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA47" s="3">
         <v>23200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>31100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>76800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>7500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>12500</v>
       </c>
-      <c r="AE47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4318,94 +4422,97 @@
       <c r="AI47" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ47" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E48" s="3">
         <v>12400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>12300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>13900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>12800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>15100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>17100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>19500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>19800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>21700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>22900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>24100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>25200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>27300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>29700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>31100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>46000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>44800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>42200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>35800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>36800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>25800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>26000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>24600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>5600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3000</v>
-      </c>
-      <c r="AC48" s="3">
-        <v>1900</v>
       </c>
       <c r="AD48" s="3">
         <v>1900</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>3</v>
+      <c r="AE48" s="3">
+        <v>1900</v>
       </c>
       <c r="AF48" s="3" t="s">
         <v>3</v>
@@ -4419,65 +4526,68 @@
       <c r="AI48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>28100</v>
+      </c>
+      <c r="E49" s="3">
         <v>28800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>29500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>27800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>23900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>24500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>25100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>25700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>26300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>26900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>27500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>28100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>28700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>29300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>29900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>30500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>44900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>46200</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4493,8 +4603,8 @@
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA49" s="3">
-        <v>0</v>
+      <c r="AA49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB49" s="3">
         <v>0</v>
@@ -4520,8 +4630,11 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4621,8 +4734,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4722,95 +4838,98 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E52" s="3">
         <v>25500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>18100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>16600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>18200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>20300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>18900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>20700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>21000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>18200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>19600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>20800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>20200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>29900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>31300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>35300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>33000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>33100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>49800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>30200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>23900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>16500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>17300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>17000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>26300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>9500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>4600</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4823,8 +4942,11 @@
       <c r="AI52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4924,95 +5046,98 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>936000</v>
+      </c>
+      <c r="E54" s="3">
         <v>998300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1080200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>881600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>919300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>665000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>794400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>849300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>546400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>655000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>503700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>625700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>623000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>728700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>862200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>813100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1012800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>781500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1081500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1093300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>703600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>787700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>905200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>989800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>631700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>640500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>325500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>401400</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5025,8 +5150,11 @@
       <c r="AI54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5062,8 +5190,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5099,95 +5228,96 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>36200</v>
+      </c>
+      <c r="E57" s="3">
         <v>18700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>26100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>27500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>9600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>13400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>18100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>11600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>10200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>8800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>10100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>11900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>12000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>22300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>10300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>8900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>9800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>12800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>13100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>8900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>10300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>16100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>12300</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5200,58 +5330,61 @@
       <c r="AI57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E58" s="3">
         <v>5300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4500</v>
-      </c>
-      <c r="H58" s="3">
-        <v>4600</v>
       </c>
       <c r="I58" s="3">
         <v>4600</v>
       </c>
       <c r="J58" s="3">
+        <v>4600</v>
+      </c>
+      <c r="K58" s="3">
         <v>4500</v>
-      </c>
-      <c r="K58" s="3">
-        <v>4100</v>
       </c>
       <c r="L58" s="3">
         <v>4100</v>
       </c>
       <c r="M58" s="3">
+        <v>4100</v>
+      </c>
+      <c r="N58" s="3">
         <v>3800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3700</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S58" s="3">
-        <v>300</v>
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T58" s="3">
         <v>300</v>
@@ -5260,14 +5393,14 @@
         <v>300</v>
       </c>
       <c r="V58" s="3">
+        <v>300</v>
+      </c>
+      <c r="W58" s="3">
         <v>3800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1600</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5283,8 +5416,8 @@
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD58" s="3">
-        <v>0</v>
+      <c r="AD58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE58" s="3">
         <v>0</v>
@@ -5301,95 +5434,98 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E59" s="3">
         <v>9100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>15000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>16100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>16200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>16600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>21500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>22700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>12100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>16800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>109900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>109000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>132400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>93400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>122900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>83500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>109300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>80500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>85100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>65900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>79800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>51800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>51500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>29600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>22600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>23100</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5402,95 +5538,98 @@
       <c r="AI59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>288000</v>
+      </c>
+      <c r="E60" s="3">
         <v>216600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>175900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>152100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>154400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>139200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>134400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>141500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>143800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>106100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>110100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>96600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>121400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>119200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>141200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>103500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>135100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>95800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>131900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>94700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>95600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>75700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>92600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>64900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>60400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>39900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>38700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>35500</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5503,95 +5642,98 @@
       <c r="AI60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1856300</v>
+      </c>
+      <c r="E61" s="3">
         <v>1854400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1853600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1853000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1726100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1725100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1724700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1724200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1735700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1730900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1729900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1725200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1707600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1698700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1693200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1708100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1705100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1376600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1375300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1362700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>477400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>471900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>466600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>461300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>91800</v>
-      </c>
-      <c r="AB61" s="3">
-        <v>75000</v>
       </c>
       <c r="AC61" s="3">
         <v>75000</v>
       </c>
       <c r="AD61" s="3">
+        <v>75000</v>
+      </c>
+      <c r="AE61" s="3">
         <v>54900</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
       <c r="AF61" s="3">
         <v>0</v>
       </c>
@@ -5604,95 +5746,98 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>855300</v>
+      </c>
+      <c r="E62" s="3">
         <v>836800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>814500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>497700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>479400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>10600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>38900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>41200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>42900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>42300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>38300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>44900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>29900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>24000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>22600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>21700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>18500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>11500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>400</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5705,8 +5850,11 @@
       <c r="AI62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5806,8 +5954,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5907,8 +6058,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6008,95 +6162,98 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3012600</v>
+      </c>
+      <c r="E66" s="3">
         <v>2921000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2858600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2520300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2377000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1883400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1876500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1886200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1888900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1848700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1853300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1839300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1877700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1867200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1887800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1854100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1883200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1524900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1545800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1488600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>645700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>623900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>639500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>609100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>223200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>180800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>162600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>149200</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6109,8 +6266,11 @@
       <c r="AI66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6146,8 +6306,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6247,8 +6408,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6348,8 +6512,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6429,13 +6596,13 @@
         <v>0</v>
       </c>
       <c r="AC70" s="3">
-        <v>479000</v>
+        <v>0</v>
       </c>
       <c r="AD70" s="3">
         <v>479000</v>
       </c>
       <c r="AE70" s="3">
-        <v>0</v>
+        <v>479000</v>
       </c>
       <c r="AF70" s="3">
         <v>0</v>
@@ -6449,8 +6616,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6550,95 +6720,98 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-3821200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-3628300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-3445600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-3263700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-3096300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2831200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2669200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2595700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2560500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2392400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2215400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-2057500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1918100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1780600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1643200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1633400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1437000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1289800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-1133900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-1037500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-888800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-768800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-652900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-531900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-440000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-366600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-319500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-230300</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6651,8 +6824,11 @@
       <c r="AI72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6752,8 +6928,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6853,8 +7032,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6954,95 +7136,98 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-2086600</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1933100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1787900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-1648400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-1467900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-1229900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-1092900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-1049500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-1354300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-1207500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-1362000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-1225700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-1254600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-1138400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-1025500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-1041000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-870400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-743400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-464300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-395300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>57900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>163800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>265800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>380700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>408500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>459800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-316100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-226900</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7055,8 +7240,11 @@
       <c r="AI76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7156,215 +7344,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AI80" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AJ80" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-192900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-182700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-181900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-167400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-265100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-162000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-73500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-35200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-168100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-177000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-157900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-140200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-137600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-137300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-9900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-196400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-147200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-155900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-96300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-163100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-120000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-115900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-121000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-91900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-73500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-60000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-127100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-61200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-31400</v>
       </c>
-      <c r="AG81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI81" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ81" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7400,16 +7597,17 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>800</v>
+      </c>
+      <c r="E83" s="3">
         <v>900</v>
-      </c>
-      <c r="E83" s="3">
-        <v>1000</v>
       </c>
       <c r="F83" s="3">
         <v>1000</v>
@@ -7427,38 +7625,38 @@
         <v>1000</v>
       </c>
       <c r="K83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L83" s="3">
         <v>1100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1700</v>
-      </c>
-      <c r="P83" s="3">
-        <v>1600</v>
       </c>
       <c r="Q83" s="3">
         <v>1600</v>
       </c>
       <c r="R83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="S83" s="3">
         <v>1900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>300</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
@@ -7477,18 +7675,18 @@
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC83" s="3">
         <v>400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>100</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF83" s="3" t="s">
         <v>3</v>
       </c>
@@ -7501,8 +7699,11 @@
       <c r="AI83" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ83" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7602,8 +7803,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7703,8 +7907,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7804,8 +8011,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7905,8 +8115,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8006,95 +8219,98 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-56400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-109600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-80700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-199200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-195300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-180600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>74700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-219500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-124800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-145200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-113400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-144300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-93200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-135200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-30500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-160600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-133900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-121600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-91700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-150800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-96300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-131700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-87800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-83900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-76200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-50000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-127400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-59100</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF89" s="3" t="s">
         <v>3</v>
       </c>
@@ -8107,8 +8323,11 @@
       <c r="AI89" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ89" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8144,34 +8363,35 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-600</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I91" s="3">
         <v>-100</v>
       </c>
       <c r="J91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K91" s="3">
         <v>-700</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-400</v>
       </c>
       <c r="L91" s="3">
         <v>-400</v>
@@ -8180,59 +8400,59 @@
         <v>-400</v>
       </c>
       <c r="N91" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="O91" s="3">
-        <v>-800</v>
+        <v>0</v>
       </c>
       <c r="P91" s="3">
         <v>-800</v>
       </c>
       <c r="Q91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="R91" s="3">
         <v>-3900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-6500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-400</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF91" s="3" t="s">
         <v>3</v>
       </c>
@@ -8245,8 +8465,11 @@
       <c r="AI91" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ91" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8346,8 +8569,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8447,95 +8673,98 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E94" s="3">
         <v>4500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-13000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>38200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>3000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>22800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>37700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>4100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>12300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>18000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>146900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>149700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>138600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>21800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>59000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-282100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>83000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-45100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-129000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>38000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-16900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-197300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF94" s="3" t="s">
         <v>3</v>
       </c>
@@ -8548,8 +8777,11 @@
       <c r="AI94" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ94" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8585,8 +8817,9 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8623,8 +8856,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -8686,8 +8919,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8787,8 +9023,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8888,8 +9127,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8989,95 +9231,98 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>302000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>60300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>473900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-5700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>279500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>307000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>150200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>6400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-20800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>325400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-135500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>547900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>4500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>439200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>42900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>367500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-11600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF100" s="3" t="s">
         <v>3</v>
       </c>
@@ -9090,8 +9335,11 @@
       <c r="AI100" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ100" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9128,8 +9376,8 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -9191,95 +9439,98 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-73000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-106000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>208400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-140500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>275400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-141600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>72000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>82800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-129400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>199500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-110500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>18200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-68900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>13100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>98500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-22200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>213300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-198000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-92600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>115100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-8700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-174000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-216100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>393300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-50200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>120200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-142000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-63200</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
@@ -9290,6 +9541,9 @@
         <v>3</v>
       </c>
       <c r="AI102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BBIO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BBIO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="92">
   <si>
     <t>BBIO</t>
   </si>
@@ -656,248 +656,252 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="36" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="37" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AI7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AJ7" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AK7" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>194500</v>
+      </c>
+      <c r="E8" s="3">
         <v>154200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>120700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>110600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>116600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>211100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>73700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>12900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>54000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>8100</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC8" s="3">
         <v>13800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>26700</v>
       </c>
-      <c r="AD8" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF8" s="3">
-        <v>0</v>
+      <c r="AE8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG8" s="3">
         <v>0</v>
       </c>
-      <c r="AH8" s="3" t="s">
-        <v>3</v>
+      <c r="AH8" s="3">
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="s">
         <v>3</v>
@@ -905,28 +909,31 @@
       <c r="AJ8" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK8" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E9" s="3">
         <v>8100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2100</v>
-      </c>
-      <c r="I9" s="3">
-        <v>600</v>
       </c>
       <c r="J9" s="3">
         <v>600</v>
@@ -944,32 +951,32 @@
         <v>600</v>
       </c>
       <c r="O9" s="3">
+        <v>600</v>
+      </c>
+      <c r="P9" s="3">
         <v>700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>600</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>700</v>
       </c>
       <c r="R9" s="3">
         <v>700</v>
       </c>
       <c r="S9" s="3">
+        <v>700</v>
+      </c>
+      <c r="T9" s="3">
         <v>1300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>100</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
@@ -985,12 +992,12 @@
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD9" s="3">
         <v>2500</v>
       </c>
-      <c r="AD9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE9" s="3" t="s">
         <v>3</v>
       </c>
@@ -1009,71 +1016,74 @@
       <c r="AJ9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>184600</v>
+      </c>
+      <c r="E10" s="3">
         <v>146100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>114100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>106900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>114000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>210500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>73000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>11300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>53900</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1089,12 +1099,12 @@
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD10" s="3">
         <v>24200</v>
       </c>
-      <c r="AD10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1113,8 +1123,11 @@
       <c r="AJ10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1151,112 +1164,116 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>126600</v>
+      </c>
+      <c r="E12" s="3">
         <v>116400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>112900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>111200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>111400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>130400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>120400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>114700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>141000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>130200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>125100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>107500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>92900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>90900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>92500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>108400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>107600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>122200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>104300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>102000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>122600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>90200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>92100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>86600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>68200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>57500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>55300</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>95200</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>42900</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>51200</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>31100</v>
       </c>
-      <c r="AH12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1359,62 +1376,65 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>11100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>8800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>21700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>4700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-47400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-123400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>21900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-20500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>5600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>7700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>5000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>8400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>22700</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1436,26 +1456,26 @@
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>400</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>2000</v>
       </c>
       <c r="AE14" s="3">
         <v>2000</v>
       </c>
       <c r="AF14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AG14" s="3">
         <v>-19300</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="3" t="s">
-        <v>3</v>
+      <c r="AH14" s="3">
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="s">
         <v>3</v>
@@ -1463,31 +1483,34 @@
       <c r="AJ14" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK14" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="E15" s="3">
         <v>1400</v>
       </c>
       <c r="F15" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="G15" s="3">
         <v>1300</v>
       </c>
       <c r="H15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I15" s="3">
         <v>1400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1500</v>
-      </c>
-      <c r="J15" s="3">
-        <v>1600</v>
       </c>
       <c r="K15" s="3">
         <v>1600</v>
@@ -1505,7 +1528,7 @@
         <v>1600</v>
       </c>
       <c r="P15" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1567,8 +1590,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1602,216 +1628,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>300500</v>
+      </c>
+      <c r="E17" s="3">
         <v>282600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>257100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>244000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>220400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>227200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>189900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>174800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>207400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>178400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>161500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>144200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>124600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>131100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>129500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>153900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>175400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>178500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>151800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>148000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>168000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>127600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>128100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>124600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>102500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>92500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>81700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>133100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>63800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>46300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>41500</v>
       </c>
-      <c r="AH17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ17" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK17" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-106000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-128400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-136400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-133500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-103800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-221300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-187100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-172600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-176700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-157400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-142600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-122800</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-129200</v>
       </c>
       <c r="Q18" s="3">
         <v>-129200</v>
       </c>
       <c r="R18" s="3">
+        <v>-129200</v>
+      </c>
+      <c r="S18" s="3">
         <v>-80200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-173700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-165600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-149500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-94000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-167500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-127500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-120000</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC18" s="3">
         <v>-78700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-55000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-133100</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF18" s="3">
+      <c r="AF18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG18" s="3">
         <v>-46300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-41500</v>
       </c>
-      <c r="AH18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ18" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK18" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1848,172 +1881,176 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E20" s="3">
         <v>9200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>13600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>7300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>15100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>8600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>8600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>8800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>97900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-7300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>28500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>6100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>3400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>700</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-7100</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF20" s="3">
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-1800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>500</v>
       </c>
-      <c r="AH20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ20" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK20" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-118800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-136200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-134300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-145800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-109800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-235000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-190400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-179600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-174600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-155700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-140900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-121500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-118900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-118700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>19300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-179100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-135600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-149700</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
@@ -2032,15 +2069,15 @@
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD21" s="3">
         <v>-58200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-139900</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF21" s="3" t="s">
         <v>3</v>
       </c>
@@ -2056,103 +2093,106 @@
       <c r="AJ21" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK21" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>52800</v>
+      </c>
+      <c r="E22" s="3">
         <v>50300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>48100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>37600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>42100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>29800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>23100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>22900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>23500</v>
-      </c>
-      <c r="L22" s="3">
-        <v>20300</v>
       </c>
       <c r="M22" s="3">
         <v>20300</v>
       </c>
       <c r="N22" s="3">
+        <v>20300</v>
+      </c>
+      <c r="O22" s="3">
         <v>20600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>20100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>20000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>19800</v>
-      </c>
-      <c r="R22" s="3">
-        <v>20300</v>
       </c>
       <c r="S22" s="3">
         <v>20300</v>
       </c>
       <c r="T22" s="3">
+        <v>20300</v>
+      </c>
+      <c r="U22" s="3">
         <v>15100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>11100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>10800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>9700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>11000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>10900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>10800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>4000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>3000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>2100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>3600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>1700</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>1200</v>
       </c>
       <c r="AG22" s="3">
         <v>1200</v>
       </c>
-      <c r="AH22" s="3" t="s">
-        <v>3</v>
+      <c r="AH22" s="3">
+        <v>1200</v>
       </c>
       <c r="AI22" s="3" t="s">
         <v>3</v>
@@ -2160,133 +2200,139 @@
       <c r="AJ22" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK22" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-166600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-194800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-186500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-181700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-169600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-266200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-164300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-75500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-36200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-170300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-179500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-160700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-142700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-140600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-140200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-201300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-152300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-161000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-102100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-171100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-135000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-130200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-136200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-104100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-84200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-60700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-143800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-69400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-49200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-42100</v>
       </c>
-      <c r="AH23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ23" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK23" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3">
         <v>-100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2100</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3">
         <v>1200</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2305,8 +2351,8 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -2368,8 +2414,11 @@
       <c r="AJ24" s="3">
         <v>0</v>
       </c>
+      <c r="AK24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2472,216 +2521,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-166600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-194600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-184900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-183800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-169600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-267400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-164300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-75500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-36200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-170300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-179500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-160700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-142700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-140600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-140200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-201300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-152300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-161000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-102100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-171100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-135000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-130200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-136200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-104100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-84200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-60700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-143800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-69400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-49200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-42100</v>
       </c>
-      <c r="AH26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ26" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK26" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-164000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-192900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-182700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-181900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-167400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-265100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-162000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-73500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-35200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-168100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-177000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-157900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-140200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-137600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-137300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-9900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-196400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-147200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-155900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-96300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-163100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-120000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-115900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-121000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-91900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-73500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-60000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-127100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-61200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-31400</v>
       </c>
-      <c r="AH27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ27" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK27" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2784,8 +2842,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2888,8 +2949,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2992,8 +3056,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3096,216 +3163,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-9200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-13600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-7300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-15100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-8600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-8600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-8800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-97900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>7300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-28500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-6100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-700</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC32" s="3">
         <v>2500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>3600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>7100</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF32" s="3">
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG32" s="3">
         <v>1800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-500</v>
       </c>
-      <c r="AH32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ32" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK32" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-164000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-192900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-182700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-181900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-167400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-265100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-162000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-73500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-35200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-168100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-177000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-157900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-140200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-137600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-137300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-9900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-196400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-147200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-155900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-96300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-163100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-120000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-115900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-121000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-91900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-73500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-60000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-127100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-61200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-31400</v>
       </c>
-      <c r="AH33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ33" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK33" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3408,221 +3484,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-164000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-192900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-182700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-181900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-167400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-265100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-162000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-73500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-35200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-168100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-177000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-157900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-140200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-137600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-137300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-9900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-196400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-147200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-155900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-96300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-163100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-120000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-115900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-121000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-91900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-73500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-60000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-127100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-61200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-31400</v>
       </c>
-      <c r="AH35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ35" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK35" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AI38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AJ38" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AK38" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3659,8 +3744,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3697,98 +3783,99 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>879900</v>
+      </c>
+      <c r="E41" s="3">
         <v>570100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>643000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>749000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>540600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>681100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>266300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>408000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>475200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>375900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>505200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>302400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>407400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>376700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>483200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>470100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>371600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>393800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>180300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>378400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>471200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>356100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>367000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>540900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>757000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>363800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>414000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>293800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>373000</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3801,23 +3888,26 @@
       <c r="AJ41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>60300</v>
+      </c>
+      <c r="E42" s="3">
         <v>17400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>7900</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
@@ -3825,68 +3915,68 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>39800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>44500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>58900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>38100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>81400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>83900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>95200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>108700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>245600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>299700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>442900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>419300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>459200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>447900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>251000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>343700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>300000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>148100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>182200</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>122100</v>
       </c>
-      <c r="AD42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3905,50 +3995,53 @@
       <c r="AJ42" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK42" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>205200</v>
+      </c>
+      <c r="E43" s="3">
         <v>139400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>116500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>76900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>115300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>235500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>8600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>10800</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
       <c r="Q43" s="3">
         <v>0</v>
       </c>
@@ -3958,27 +4051,27 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U43" s="3">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V43" s="3">
         <v>500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>10200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>500</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y43" s="3">
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z43" s="3">
         <v>8000</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3994,8 +4087,8 @@
       <c r="AE43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF43" s="3">
-        <v>0</v>
+      <c r="AF43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG43" s="3">
         <v>0</v>
@@ -4009,26 +4102,29 @@
       <c r="AJ43" s="3">
         <v>0</v>
       </c>
+      <c r="AK43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E44" s="3">
         <v>26800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>24500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>18300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4000</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I44" s="3" t="s">
         <v>3</v>
       </c>
@@ -4050,8 +4146,8 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -4113,32 +4209,35 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E45" s="3">
         <v>5100</v>
-      </c>
-      <c r="E45" s="3">
-        <v>4900</v>
       </c>
       <c r="F45" s="3">
         <v>4900</v>
       </c>
       <c r="G45" s="3">
+        <v>4900</v>
+      </c>
+      <c r="H45" s="3">
         <v>3100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>9500</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4154,57 +4253,57 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>76900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>50200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>55600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>45000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>52200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>39600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>62000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>25500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>35700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>26700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>21000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>19800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>22600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>22100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>12900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>9400</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4217,98 +4316,101 @@
       <c r="AJ45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1241300</v>
+      </c>
+      <c r="E46" s="3">
         <v>797700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>839400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>912300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>695200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>720700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>444600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>616200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>783400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>477600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>587700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>432900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>552700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>548900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>642200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>771300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>716200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>888900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>639700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>909900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>945100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>642800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>745400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>861900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>925000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>568600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>558200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>306700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>382500</v>
       </c>
-      <c r="AF46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4321,52 +4423,55 @@
       <c r="AJ46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>61500</v>
+      </c>
+      <c r="E47" s="3">
         <v>80000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>92200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>108000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>128200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>143700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>160400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>117000</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3">
         <v>1600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>800</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -4374,45 +4479,45 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U47" s="3">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V47" s="3">
         <v>17700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>79600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>82200</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB47" s="3">
         <v>23200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>31100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>76800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>7500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>12500</v>
       </c>
-      <c r="AF47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4425,97 +4530,100 @@
       <c r="AJ47" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK47" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>22200</v>
+      </c>
+      <c r="E48" s="3">
         <v>13500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>12400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>12300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>13900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>12800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>15100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>17100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>19500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>19800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>21700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>22900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>24100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>25200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>27300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>29700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>31100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>46000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>44800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>42200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>35800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>36800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>25800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>26000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>24600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3000</v>
-      </c>
-      <c r="AD48" s="3">
-        <v>1900</v>
       </c>
       <c r="AE48" s="3">
         <v>1900</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>3</v>
+      <c r="AF48" s="3">
+        <v>1900</v>
       </c>
       <c r="AG48" s="3" t="s">
         <v>3</v>
@@ -4529,68 +4637,71 @@
       <c r="AJ48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>27400</v>
+      </c>
+      <c r="E49" s="3">
         <v>28100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>28800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>29500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>27800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>23900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>24500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>25100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>25700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>26300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>26900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>27500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>28100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>28700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>29300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>29900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>30500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>44900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>46200</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4606,8 +4717,8 @@
       <c r="AA49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB49" s="3">
-        <v>0</v>
+      <c r="AB49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC49" s="3">
         <v>0</v>
@@ -4633,8 +4744,11 @@
       <c r="AJ49" s="3">
         <v>0</v>
       </c>
+      <c r="AK49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4737,8 +4851,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4841,98 +4958,101 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E52" s="3">
         <v>16700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>25500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>18100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>16600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>18200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>20300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>18900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>20700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>21000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>18200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>19600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>20800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>20200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>29900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>31300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>35300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>33000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>33100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>49800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>30200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>23900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>16500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>17300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>17000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>26300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>9500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>4600</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4945,8 +5065,11 @@
       <c r="AJ52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5049,98 +5172,101 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1371000</v>
+      </c>
+      <c r="E54" s="3">
         <v>936000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>998300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1080200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>881600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>919300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>665000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>794400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>849300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>546400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>655000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>503700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>625700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>623000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>728700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>862200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>813100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1012800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>781500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1081500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1093300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>703600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>787700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>905200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>989800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>631700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>640500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>325500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>401400</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5153,8 +5279,11 @@
       <c r="AJ54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5191,8 +5320,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5229,98 +5359,99 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E57" s="3">
         <v>36200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>18700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>26100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>27500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>9600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>13400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>18100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>11600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>10200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>8800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>10100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>11900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>12000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>22300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>10300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>8900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>9800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>12800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>13100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>8900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>10300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>16100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>12300</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5333,61 +5464,64 @@
       <c r="AJ57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>551900</v>
+      </c>
+      <c r="E58" s="3">
         <v>6200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4500</v>
-      </c>
-      <c r="I58" s="3">
-        <v>4600</v>
       </c>
       <c r="J58" s="3">
         <v>4600</v>
       </c>
       <c r="K58" s="3">
+        <v>4600</v>
+      </c>
+      <c r="L58" s="3">
         <v>4500</v>
-      </c>
-      <c r="L58" s="3">
-        <v>4100</v>
       </c>
       <c r="M58" s="3">
         <v>4100</v>
       </c>
       <c r="N58" s="3">
+        <v>4100</v>
+      </c>
+      <c r="O58" s="3">
         <v>3800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3700</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T58" s="3">
-        <v>300</v>
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U58" s="3">
         <v>300</v>
@@ -5396,14 +5530,14 @@
         <v>300</v>
       </c>
       <c r="W58" s="3">
+        <v>300</v>
+      </c>
+      <c r="X58" s="3">
         <v>3800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1600</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5419,8 +5553,8 @@
       <c r="AD58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE58" s="3">
-        <v>0</v>
+      <c r="AE58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF58" s="3">
         <v>0</v>
@@ -5437,98 +5571,101 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E59" s="3">
         <v>7200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>9100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>15000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>16100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>16200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>16600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>21500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>22700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>12600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>16800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>109900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>109000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>132400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>93400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>122900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>83500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>109300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>80500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>85100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>65900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>79800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>51800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>51500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>29600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>22600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>23100</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5541,98 +5678,101 @@
       <c r="AJ59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>816400</v>
+      </c>
+      <c r="E60" s="3">
         <v>288000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>216600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>175900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>152100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>154400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>139200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>134400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>141500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>143800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>106100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>110100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>96600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>121400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>119200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>141200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>103500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>135100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>95800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>131900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>94700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>95600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>75700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>92600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>64900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>60400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>39900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>38700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>35500</v>
       </c>
-      <c r="AF60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5645,98 +5785,101 @@
       <c r="AJ60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1940300</v>
+      </c>
+      <c r="E61" s="3">
         <v>1856300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1854400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1853600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1853000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1726100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1725100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1724700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1724200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1735700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1730900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1729900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1725200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1707600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1698700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1693200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1708100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1705100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1376600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1375300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1362700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>477400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>471900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>466600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>461300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>91800</v>
-      </c>
-      <c r="AC61" s="3">
-        <v>75000</v>
       </c>
       <c r="AD61" s="3">
         <v>75000</v>
       </c>
       <c r="AE61" s="3">
+        <v>75000</v>
+      </c>
+      <c r="AF61" s="3">
         <v>54900</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
       <c r="AG61" s="3">
         <v>0</v>
       </c>
@@ -5749,98 +5892,101 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>871400</v>
+      </c>
+      <c r="E62" s="3">
         <v>855300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>836800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>814500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>497700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>479400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>10600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>38900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>41200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>42900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>42300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>38300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>44900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>29900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>24000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>22600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>21700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>18500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>11500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>400</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5853,8 +5999,11 @@
       <c r="AJ62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5957,8 +6106,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6061,8 +6213,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6165,98 +6320,101 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3639900</v>
+      </c>
+      <c r="E66" s="3">
         <v>3012600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2921000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2858600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2520300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2377000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1883400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1876500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1886200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1888900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1848700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1853300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1839300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1877700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1867200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1887800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1854100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1883200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1524900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1545800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1488600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>645700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>623900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>639500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>609100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>223200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>180800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>162600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>149200</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6269,8 +6427,11 @@
       <c r="AJ66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6307,8 +6468,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6411,8 +6573,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6515,8 +6680,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6599,13 +6767,13 @@
         <v>0</v>
       </c>
       <c r="AD70" s="3">
-        <v>479000</v>
+        <v>0</v>
       </c>
       <c r="AE70" s="3">
         <v>479000</v>
       </c>
       <c r="AF70" s="3">
-        <v>0</v>
+        <v>479000</v>
       </c>
       <c r="AG70" s="3">
         <v>0</v>
@@ -6619,8 +6787,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6723,98 +6894,101 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-3985200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-3821200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-3628300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-3445600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-3263700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-3096300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2831200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2669200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2595700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2560500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2392400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-2215400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-2057500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1918100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1780600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1643200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1633400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1437000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-1289800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-1133900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-1037500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-888800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-768800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-652900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-531900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-440000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-366600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-319500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-230300</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6827,8 +7001,11 @@
       <c r="AJ72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6931,8 +7108,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7035,8 +7215,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7139,98 +7322,101 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-2278400</v>
+      </c>
+      <c r="E76" s="3">
         <v>-2086600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1933100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-1787900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-1648400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-1467900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-1229900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-1092900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-1049500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-1354300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-1207500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-1362000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-1225700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-1254600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-1138400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-1025500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-1041000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-870400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-743400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-464300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-395300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>57900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>163800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>265800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>380700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>408500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>459800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-316100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-226900</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7243,8 +7429,11 @@
       <c r="AJ76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7347,221 +7536,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AI80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AJ80" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AK80" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-164000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-192900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-182700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-181900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-167400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-265100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-162000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-73500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-35200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-168100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-177000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-157900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-140200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-137600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-137300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-9900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-196400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-147200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-155900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-96300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-163100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-120000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-115900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-121000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-91900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-73500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-60000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-127100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-61200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-31400</v>
       </c>
-      <c r="AH81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ81" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK81" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7598,19 +7796,20 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>700</v>
+      </c>
+      <c r="E83" s="3">
         <v>800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>900</v>
-      </c>
-      <c r="F83" s="3">
-        <v>1000</v>
       </c>
       <c r="G83" s="3">
         <v>1000</v>
@@ -7628,38 +7827,38 @@
         <v>1000</v>
       </c>
       <c r="L83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M83" s="3">
         <v>1100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1700</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>1600</v>
       </c>
       <c r="R83" s="3">
         <v>1600</v>
       </c>
       <c r="S83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="T83" s="3">
         <v>1900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>300</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
@@ -7678,18 +7877,18 @@
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD83" s="3">
         <v>400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>100</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG83" s="3" t="s">
         <v>3</v>
       </c>
@@ -7702,8 +7901,11 @@
       <c r="AJ83" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK83" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7806,8 +8008,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7910,8 +8115,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8014,8 +8222,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8118,8 +8329,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8222,98 +8436,101 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-197300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-56400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-109600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-80700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-199200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-195300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-180600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>74700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-219500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-124800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-145200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-113400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-144300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-93200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-135200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-30500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-160600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-133900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-121600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-91700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-150800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-96300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-131700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-87800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-83900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-76200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-50000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-127400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-59100</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG89" s="3" t="s">
         <v>3</v>
       </c>
@@ -8326,8 +8543,11 @@
       <c r="AJ89" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK89" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8364,37 +8584,38 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-600</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J91" s="3">
         <v>-100</v>
       </c>
       <c r="K91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L91" s="3">
         <v>-700</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-400</v>
       </c>
       <c r="M91" s="3">
         <v>-400</v>
@@ -8403,59 +8624,59 @@
         <v>-400</v>
       </c>
       <c r="O91" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="P91" s="3">
-        <v>-800</v>
+        <v>0</v>
       </c>
       <c r="Q91" s="3">
         <v>-800</v>
       </c>
       <c r="R91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="S91" s="3">
         <v>-3900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-6500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-400</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG91" s="3" t="s">
         <v>3</v>
       </c>
@@ -8468,8 +8689,11 @@
       <c r="AJ91" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK91" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8572,8 +8796,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8676,98 +8903,101 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-42700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-14400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>4500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-13000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>38200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>3000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>22800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>37700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>4100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>12300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>18000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>146900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>149700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>138600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>21800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>59000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-282100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>83000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-45100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-129000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>38000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-16900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-197300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG94" s="3" t="s">
         <v>3</v>
       </c>
@@ -8780,8 +9010,11 @@
       <c r="AJ94" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK94" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8818,8 +9051,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8859,8 +9093,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -8922,8 +9156,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9026,8 +9263,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9130,8 +9370,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9234,98 +9477,101 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>549900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>302000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>60300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>473900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-5700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>279500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>307000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>150200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>6400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-20800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>325400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-135500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>547900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>4500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>439200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>42900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>367500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-11600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG100" s="3" t="s">
         <v>3</v>
       </c>
@@ -9338,8 +9584,11 @@
       <c r="AJ100" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK100" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9379,8 +9628,8 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -9442,98 +9691,101 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>309900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-73000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-106000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>208400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-140500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>275400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-141600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>72000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>82800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-129400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>199500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-110500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>18200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-68900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>13100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>98500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-22200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>213300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-198000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-92600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>115100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-8700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-174000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-216100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>393300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-50200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>120200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-142000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-63200</v>
       </c>
-      <c r="AF102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG102" s="3" t="s">
         <v>3</v>
       </c>
@@ -9544,6 +9796,9 @@
         <v>3</v>
       </c>
       <c r="AJ102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
